--- a/output/yearly_surface_area_iteration_6_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_6_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497656940133</v>
+        <v>10.84497631369879</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907276837963</v>
+        <v>37.78907187738996</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.710425484976196</v>
+        <v>4.119413367019616</v>
       </c>
       <c r="C2" t="n">
-        <v>7.223699607848031</v>
+        <v>17.71760081854219</v>
       </c>
       <c r="D2" t="n">
-        <v>19.60648340151305</v>
+        <v>29.00573592197201</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.19392838155114</v>
+        <v>16.13502351929633</v>
       </c>
       <c r="C3" t="n">
-        <v>22.40348261091221</v>
+        <v>36.56028450615122</v>
       </c>
       <c r="D3" t="n">
-        <v>55.66509483079415</v>
+        <v>76.43396751413542</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.16580185549325</v>
+        <v>33.32346232524949</v>
       </c>
       <c r="C4" t="n">
-        <v>56.80686741083319</v>
+        <v>60.34214089382595</v>
       </c>
       <c r="D4" t="n">
-        <v>76.92091437544184</v>
+        <v>88.89234588102745</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.58897617375263</v>
+        <v>39.98167525545136</v>
       </c>
       <c r="C5" t="n">
-        <v>95.22952731194061</v>
+        <v>113.588209381356</v>
       </c>
       <c r="D5" t="n">
-        <v>59.88660995905545</v>
+        <v>59.15029918087033</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.69692736349078</v>
+        <v>36.14598697495907</v>
       </c>
       <c r="C6" t="n">
-        <v>113.0266496945268</v>
+        <v>164.3475109340288</v>
       </c>
       <c r="D6" t="n">
-        <v>45.32336451425826</v>
+        <v>41.66046382971341</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.37385025333556</v>
+        <v>24.79305652304895</v>
       </c>
       <c r="C7" t="n">
-        <v>116.4195697604038</v>
+        <v>170.9762714331032</v>
       </c>
       <c r="D7" t="n">
-        <v>38.98618308334508</v>
+        <v>37.36924461445059</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.68418033886879</v>
+        <v>12.85107744859075</v>
       </c>
       <c r="C8" t="n">
-        <v>93.37893288943536</v>
+        <v>122.0852357616121</v>
       </c>
       <c r="D8" t="n">
-        <v>35.9663271450819</v>
+        <v>34.88149593188918</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.989061906533041</v>
+        <v>6.767186925373262</v>
       </c>
       <c r="C9" t="n">
-        <v>53.24999547834697</v>
+        <v>59.46249495082079</v>
       </c>
       <c r="D9" t="n">
-        <v>33.9468721174462</v>
+        <v>33.72499713628642</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.409429850399925</v>
+        <v>5.267076433284139</v>
       </c>
       <c r="C10" t="n">
-        <v>32.88363935374691</v>
+        <v>33.16834618797849</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01894061048373</v>
+        <v>34.59188035913637</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>29.67528785626833</v>
+        <v>28.96450251839364</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>35.7169632282032</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.77167905773377</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.49763257952867</v>
       </c>
     </row>
     <row r="13">
@@ -937,7 +937,7 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.49598787928967</v>
+        <v>25.23582473766426</v>
       </c>
       <c r="D13" t="n">
         <v>32.5203927031756</v>
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.66110142005238</v>
+        <v>23.04652735719387</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -962,13 +962,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>21.50027472300514</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>18.59921025695582</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -993,7 +993,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.9443845382232</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
         <v>24.0832529328785</v>
@@ -1010,7 +1010,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1024,7 +1024,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.693163193126233</v>
+        <v>7.642201151489</v>
       </c>
       <c r="C21" t="n">
-        <v>94.24124911579635</v>
+        <v>92.66168896180412</v>
       </c>
       <c r="D21" t="n">
-        <v>8.654808592267013</v>
+        <v>7.642201151489</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.021459580773187</v>
+        <v>5.259222451650163</v>
       </c>
       <c r="C2" t="n">
-        <v>8.043458940894118</v>
+        <v>18.9762013753866</v>
       </c>
       <c r="D2" t="n">
-        <v>27.8394196493268</v>
+        <v>28.52762479000382</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.96321767105314</v>
+        <v>14.80966411856313</v>
       </c>
       <c r="C3" t="n">
-        <v>25.2701859073129</v>
+        <v>51.9099098620501</v>
       </c>
       <c r="D3" t="n">
-        <v>57.68258636302135</v>
+        <v>80.19896995992195</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.5959872764026</v>
+        <v>31.53668150352029</v>
       </c>
       <c r="C4" t="n">
-        <v>55.78584979841651</v>
+        <v>74.16416682191679</v>
       </c>
       <c r="D4" t="n">
-        <v>84.91037719260238</v>
+        <v>102.20386300291</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.89041377668541</v>
+        <v>44.00684084286328</v>
       </c>
       <c r="C5" t="n">
-        <v>99.96645998493149</v>
+        <v>112.287393673229</v>
       </c>
       <c r="D5" t="n">
-        <v>72.42843688080845</v>
+        <v>74.51465075233293</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>43.55229165579701</v>
+        <v>43.75354993516761</v>
       </c>
       <c r="C6" t="n">
-        <v>130.656874967391</v>
+        <v>170.465762626895</v>
       </c>
       <c r="D6" t="n">
-        <v>52.36740429222912</v>
+        <v>48.66425195181016</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>32.75797564760332</v>
+        <v>32.99752208743954</v>
       </c>
       <c r="C7" t="n">
-        <v>140.1945539141488</v>
+        <v>201.8777621719759</v>
       </c>
       <c r="D7" t="n">
-        <v>42.99858595060179</v>
+        <v>40.60312155223958</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19.10971906316416</v>
+        <v>18.77592484372025</v>
       </c>
       <c r="C8" t="n">
-        <v>123.6707583039707</v>
+        <v>167.4812496059846</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>36.46701847424777</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.762499171030278</v>
+        <v>9.429686699290611</v>
       </c>
       <c r="C9" t="n">
-        <v>82.53749299143782</v>
+        <v>99.06717908784135</v>
       </c>
       <c r="D9" t="n">
-        <v>35.61093447614454</v>
+        <v>35.05624702324509</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.121196935978863</v>
+        <v>5.836490101747287</v>
       </c>
       <c r="C10" t="n">
-        <v>47.40368789955724</v>
+        <v>49.53898915629405</v>
       </c>
       <c r="D10" t="n">
-        <v>35.44600086183109</v>
+        <v>34.87658719336794</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>33.7623035490478</v>
+        <v>33.05151821117311</v>
       </c>
       <c r="D11" t="n">
-        <v>37.13853390395258</v>
+        <v>36.25005223160922</v>
       </c>
     </row>
     <row r="12">
@@ -1234,7 +1234,7 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>30.8092064546734</v>
+        <v>29.72437524148068</v>
       </c>
       <c r="D12" t="n">
         <v>34.71459882216721</v>
@@ -1248,7 +1248,7 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>27.83745615391831</v>
+        <v>27.3171298706675</v>
       </c>
       <c r="D13" t="n">
         <v>33.04071898642641</v>
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>25.81211064005714</v>
+        <v>24.89024954576939</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -1273,13 +1273,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>23.29196428325557</v>
+        <v>22.57528845915541</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -1287,13 +1287,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>20.66578917439536</v>
+        <v>19.83915760741954</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -1304,7 +1304,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>18.41660518396592</v>
       </c>
       <c r="D17" t="n">
         <v>24.0832529328785</v>
@@ -1318,10 +1318,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1335,7 +1335,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.878549869934493</v>
+        <v>7.810281236258569</v>
       </c>
       <c r="C21" t="n">
-        <v>103.4059670428902</v>
+        <v>100.5573709168291</v>
       </c>
       <c r="D21" t="n">
-        <v>9.848187337418116</v>
+        <v>8.78656639079089</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.779368808451725</v>
+        <v>6.08192702780899</v>
       </c>
       <c r="C2" t="n">
-        <v>10.44972256400305</v>
+        <v>14.09691528527995</v>
       </c>
       <c r="D2" t="n">
-        <v>28.9006889176176</v>
+        <v>28.61696383109027</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.24716374175872</v>
+        <v>15.56070111231194</v>
       </c>
       <c r="C3" t="n">
-        <v>27.97490083251286</v>
+        <v>61.5408548407113</v>
       </c>
       <c r="D3" t="n">
-        <v>64.32901832077225</v>
+        <v>83.32583639794802</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.00064725700153</v>
+        <v>29.21386643527233</v>
       </c>
       <c r="C4" t="n">
-        <v>59.09139431861551</v>
+        <v>96.42235077260048</v>
       </c>
       <c r="D4" t="n">
-        <v>92.31275488262334</v>
+        <v>112.4012764069216</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.41212271826797</v>
+        <v>44.79223900626073</v>
       </c>
       <c r="C5" t="n">
-        <v>100.0646347553562</v>
+        <v>120.80405500757</v>
       </c>
       <c r="D5" t="n">
-        <v>82.61406931236911</v>
+        <v>87.91550691530188</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>51.32086123950202</v>
+        <v>49.46928506929254</v>
       </c>
       <c r="C6" t="n">
-        <v>142.2091002032632</v>
+        <v>172.5991003882233</v>
       </c>
       <c r="D6" t="n">
-        <v>61.22276858453534</v>
+        <v>57.88188114698346</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>40.90255460203486</v>
+        <v>40.24380189248525</v>
       </c>
       <c r="C7" t="n">
-        <v>162.9514656985898</v>
+        <v>221.520570238546</v>
       </c>
       <c r="D7" t="n">
-        <v>46.8912155979404</v>
+        <v>43.83699849002857</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>26.11939767148639</v>
+        <v>25.2849121228766</v>
       </c>
       <c r="C8" t="n">
-        <v>151.2087814080937</v>
+        <v>207.0358646100886</v>
       </c>
       <c r="D8" t="n">
-        <v>40.47254910757476</v>
+        <v>38.63668090063322</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>13.86718632248619</v>
+        <v>13.09062388842696</v>
       </c>
       <c r="C9" t="n">
-        <v>114.487490278446</v>
+        <v>141.5562379799391</v>
       </c>
       <c r="D9" t="n">
-        <v>36.72030938194344</v>
+        <v>35.83280945730432</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>68.61434704980958</v>
+        <v>75.58966448848317</v>
       </c>
       <c r="D10" t="n">
-        <v>36.01541453029424</v>
+        <v>35.58835427894688</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.153193699591506</v>
+        <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
         <v>42.46942393801276</v>
       </c>
       <c r="D11" t="n">
-        <v>37.49392657288993</v>
+        <v>36.25005223160922</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>34.28066633689012</v>
+        <v>32.54493639578176</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>35.36549755008285</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>30.43908757017236</v>
+        <v>29.39843500367074</v>
       </c>
       <c r="D13" t="n">
-        <v>33.56104526967722</v>
+        <v>33.04071898642641</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>27.04125876577415</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>25.083653843506</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>22.31905230834699</v>
+        <v>21.07910495788326</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -1612,10 +1612,10 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>19.83326712119407</v>
+        <v>19.36104647545135</v>
       </c>
       <c r="D17" t="n">
         <v>24.0832529328785</v>
@@ -1629,10 +1629,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1646,7 +1646,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.048727697533895</v>
+        <v>7.961247375100001</v>
       </c>
       <c r="C21" t="n">
-        <v>111.6760968032828</v>
+        <v>107.47683956385</v>
       </c>
       <c r="D21" t="n">
-        <v>11.0670005841091</v>
+        <v>9.951559218875001</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.0175325899562</v>
+        <v>5.613633372883262</v>
       </c>
       <c r="C2" t="n">
-        <v>7.021459580773187</v>
+        <v>9.92350579452676</v>
       </c>
       <c r="D2" t="n">
-        <v>23.38326681975053</v>
+        <v>23.8525422223805</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.61946710584651</v>
+        <v>19.1146278016854</v>
       </c>
       <c r="C3" t="n">
-        <v>42.48513190128072</v>
+        <v>82.22137023067037</v>
       </c>
       <c r="D3" t="n">
-        <v>71.00490270965057</v>
+        <v>88.88743714250622</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.29647211114931</v>
+        <v>21.51794618168159</v>
       </c>
       <c r="C4" t="n">
-        <v>83.41713893444297</v>
+        <v>110.282664861157</v>
       </c>
       <c r="D4" t="n">
-        <v>90.42387229965247</v>
+        <v>104.3224745486746</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.91246989006857</v>
+        <v>27.85709110800325</v>
       </c>
       <c r="C5" t="n">
-        <v>84.97026380256145</v>
+        <v>103.1325963311275</v>
       </c>
       <c r="D5" t="n">
-        <v>59.56754195517523</v>
+        <v>57.35860962061991</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>25.39879485656924</v>
+        <v>24.95602664195392</v>
       </c>
       <c r="C6" t="n">
-        <v>107.3109145604019</v>
+        <v>145.9122525436822</v>
       </c>
       <c r="D6" t="n">
-        <v>30.87302005544945</v>
+        <v>28.86043726174349</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.30723027816702</v>
+        <v>16.70836417857646</v>
       </c>
       <c r="C7" t="n">
-        <v>106.2987326773234</v>
+        <v>145.5843488104638</v>
       </c>
       <c r="D7" t="n">
-        <v>28.44613973055133</v>
+        <v>27.12863431145211</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>9.095892479846697</v>
       </c>
       <c r="C8" t="n">
-        <v>84.36648896444964</v>
+        <v>104.3106935762236</v>
       </c>
       <c r="D8" t="n">
-        <v>27.03733177495716</v>
+        <v>26.36974333606933</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.324999547834698</v>
+        <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
-        <v>52.36249555370786</v>
+        <v>57.68749510154256</v>
       </c>
       <c r="D9" t="n">
-        <v>27.40156017323271</v>
+        <v>27.17968519207294</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.701188845010476</v>
+        <v>3.558835427894688</v>
       </c>
       <c r="C10" t="n">
         <v>33.31069960509428</v>
       </c>
       <c r="D10" t="n">
-        <v>29.32480392585223</v>
+        <v>28.32833000604172</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>26.12136116689488</v>
       </c>
       <c r="D11" t="n">
-        <v>28.07602084605028</v>
+        <v>28.25371718051895</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>23.86628669023996</v>
       </c>
       <c r="D12" t="n">
-        <v>27.33774657245668</v>
+        <v>26.90381408717959</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>22.37403017978481</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>24.97566159603886</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>20.89551813718911</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>23.96838845148163</v>
+        <v>24.58296251434014</v>
       </c>
     </row>
     <row r="15">
@@ -1895,13 +1895,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0.3583379120500857</v>
       </c>
       <c r="C15" t="n">
-        <v>18.63357142660446</v>
+        <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
-        <v>22.57528845915541</v>
+        <v>22.21695054710532</v>
       </c>
     </row>
     <row r="16">
@@ -1909,10 +1909,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>16.94594712300419</v>
+        <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
         <v>20.25247339090745</v>
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>15.58328130950962</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>17.47216389248049</v>
       </c>
     </row>
     <row r="18">
@@ -1943,7 +1943,7 @@
         <v>16.05157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>13.37631247036279</v>
       </c>
     </row>
     <row r="19">
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>74.64718669240621</v>
+        <v>72.62969516017901</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>6.724971774090649</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.098796665230434</v>
+        <v>3.413536767666159</v>
       </c>
       <c r="C2" t="n">
-        <v>3.571598148049896</v>
+        <v>4.435536127787089</v>
       </c>
       <c r="D2" t="n">
-        <v>17.5124155483546</v>
+        <v>17.10302675568368</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.03318379996192</v>
+        <v>19.6055016538088</v>
       </c>
       <c r="C3" t="n">
-        <v>35.40182221513998</v>
+        <v>62.07099860100459</v>
       </c>
       <c r="D3" t="n">
-        <v>73.15493018195109</v>
+        <v>87.79769719079225</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.58773238414112</v>
+        <v>27.6568145763369</v>
       </c>
       <c r="C4" t="n">
-        <v>96.80523237725674</v>
+        <v>157.9258992005504</v>
       </c>
       <c r="D4" t="n">
-        <v>103.8757793432423</v>
+        <v>121.3989941163436</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.47130531796326</v>
+        <v>30.99868376159304</v>
       </c>
       <c r="C5" t="n">
-        <v>119.1350839103505</v>
+        <v>147.753029489145</v>
       </c>
       <c r="D5" t="n">
-        <v>73.16474765899356</v>
+        <v>73.21383504420589</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.75226508782709</v>
+        <v>29.02144388523996</v>
       </c>
       <c r="C6" t="n">
-        <v>125.1826497685108</v>
+        <v>160.8053652171063</v>
       </c>
       <c r="D6" t="n">
-        <v>37.79630486579796</v>
+        <v>34.97868895460962</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.28915790886308</v>
+        <v>15.57051858935441</v>
       </c>
       <c r="C7" t="n">
-        <v>129.1754176816825</v>
+        <v>175.8270868397867</v>
       </c>
       <c r="D7" t="n">
-        <v>31.02126395879071</v>
+        <v>29.58398531977338</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.17795837637593</v>
+        <v>7.677267047210056</v>
       </c>
       <c r="C8" t="n">
-        <v>108.1493270998286</v>
+        <v>133.2673421129833</v>
       </c>
       <c r="D8" t="n">
-        <v>28.20561154301086</v>
+        <v>27.12078032981814</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.437499623195581</v>
+        <v>4.104687151455913</v>
       </c>
       <c r="C9" t="n">
-        <v>58.90780749792134</v>
+        <v>59.79530742256046</v>
       </c>
       <c r="D9" t="n">
-        <v>28.51093507903161</v>
+        <v>28.06718511671205</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>35.3036474447153</v>
+        <v>34.44952694202058</v>
       </c>
       <c r="D10" t="n">
-        <v>30.32127784566274</v>
+        <v>29.46715734296802</v>
       </c>
     </row>
     <row r="11">
@@ -2150,10 +2150,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>29.852984190737</v>
+        <v>28.60910984945629</v>
       </c>
       <c r="D11" t="n">
         <v>29.31989518733098</v>
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>21.47965802121596</v>
+        <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>27.77167905773377</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>17.17076734727672</v>
+        <v>16.3902779224005</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -2192,13 +2192,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>15.36435157146258</v>
+        <v>14.74977750860408</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>18.4372218857551</v>
       </c>
     </row>
     <row r="15">
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>14.33351648200343</v>
+        <v>13.97517856995334</v>
       </c>
       <c r="D15" t="n">
         <v>17.20021977840412</v>
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>13.22610507161303</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -2240,7 +2240,7 @@
         <v>13.69439872653876</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>11.33329549782518</v>
       </c>
     </row>
     <row r="18">
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>64.99562501195582</v>
+        <v>63.19019098384595</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>5.416302084329653</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.828235209485814</v>
+        <v>2.774419012201486</v>
       </c>
       <c r="C2" t="n">
-        <v>5.464407721837746</v>
+        <v>5.677446973659304</v>
       </c>
       <c r="D2" t="n">
-        <v>19.68895020866978</v>
+        <v>18.59822850925158</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.09008410907923</v>
+        <v>15.64905840569416</v>
       </c>
       <c r="C3" t="n">
-        <v>23.88101290580366</v>
+        <v>39.67733346713484</v>
       </c>
       <c r="D3" t="n">
-        <v>70.19496085364695</v>
+        <v>81.74522259411067</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.50512670826415</v>
+        <v>32.00890214926301</v>
       </c>
       <c r="C4" t="n">
-        <v>92.41485664386501</v>
+        <v>156.2284574199077</v>
       </c>
       <c r="D4" t="n">
-        <v>115.6302446061893</v>
+        <v>134.1234261110865</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.58897617375263</v>
+        <v>35.4901795085222</v>
       </c>
       <c r="C5" t="n">
-        <v>148.8084082712103</v>
+        <v>213.5301256736813</v>
       </c>
       <c r="D5" t="n">
-        <v>91.59706080622742</v>
+        <v>94.05143006684445</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.23278168356029</v>
+        <v>34.25415914887547</v>
       </c>
       <c r="C6" t="n">
-        <v>157.5047294354285</v>
+        <v>195.3010343012265</v>
       </c>
       <c r="D6" t="n">
-        <v>49.91205328390785</v>
+        <v>45.92713935237005</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.43373686329462</v>
+        <v>22.57725195456389</v>
       </c>
       <c r="C7" t="n">
-        <v>155.525526063667</v>
+        <v>201.2190094624262</v>
       </c>
       <c r="D7" t="n">
-        <v>34.37491411649782</v>
+        <v>32.09922293805371</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.93314334511998</v>
+        <v>10.6814150222053</v>
       </c>
       <c r="C8" t="n">
-        <v>138.6914981789469</v>
+        <v>177.1612819698582</v>
       </c>
       <c r="D8" t="n">
-        <v>30.20837685967435</v>
+        <v>28.45595720759379</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>91.85624220014853</v>
+        <v>102.2843663146582</v>
       </c>
       <c r="D9" t="n">
-        <v>29.17656002251095</v>
+        <v>28.6218725696115</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.704714925199962</v>
+        <v>2.420008090968388</v>
       </c>
       <c r="C10" t="n">
-        <v>50.1084028247572</v>
+        <v>47.97310156802039</v>
       </c>
       <c r="D10" t="n">
-        <v>30.89069151412589</v>
+        <v>30.03657101143117</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>34.82848155585983</v>
+        <v>33.22921454564179</v>
       </c>
       <c r="D11" t="n">
-        <v>30.03068052520567</v>
+        <v>29.852984190737</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>26.03594911662541</v>
+        <v>24.0832529328785</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>28.20561154301086</v>
       </c>
     </row>
     <row r="13">
@@ -2489,13 +2489,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.2601631416254048</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>19.51223562190536</v>
+        <v>18.47158305540374</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>26.01631416254048</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.90078672860884</v>
+        <v>15.67163860289184</v>
       </c>
       <c r="D14" t="n">
-        <v>19.66637001147211</v>
+        <v>19.0517959486136</v>
       </c>
     </row>
     <row r="15">
@@ -2523,7 +2523,7 @@
         <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>16.84188186635403</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.87936820556466</v>
+        <v>14.05273663858884</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -2551,7 +2551,7 @@
         <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
-        <v>11.33329549782518</v>
+        <v>10.38885420633975</v>
       </c>
     </row>
     <row r="18">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>35.50686921949439</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>3.610868056219768</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.807798434145878</v>
+        <v>1.701368771459722</v>
       </c>
       <c r="C2" t="n">
-        <v>2.519164609097316</v>
+        <v>2.810743677258618</v>
       </c>
       <c r="D2" t="n">
-        <v>13.60604143315654</v>
+        <v>13.12007631955437</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.61531913085127</v>
+        <v>14.75075925630833</v>
       </c>
       <c r="C3" t="n">
-        <v>24.29825568010856</v>
+        <v>35.13675033499334</v>
       </c>
       <c r="D3" t="n">
-        <v>71.6724911485384</v>
+        <v>81.12181280191395</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.7551125199486</v>
+        <v>34.9953786655818</v>
       </c>
       <c r="C4" t="n">
-        <v>89.17312572444203</v>
+        <v>152.1826751307066</v>
       </c>
       <c r="D4" t="n">
-        <v>124.0791653489374</v>
+        <v>143.4402118243887</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.15977250054753</v>
+        <v>36.61918936840603</v>
       </c>
       <c r="C5" t="n">
-        <v>175.8555575232099</v>
+        <v>266.1763463139165</v>
       </c>
       <c r="D5" t="n">
-        <v>99.45104244020192</v>
+        <v>96.72669256091702</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.63151012020474</v>
+        <v>26.96860943565989</v>
       </c>
       <c r="C6" t="n">
-        <v>196.3073256980795</v>
+        <v>227.2608490652772</v>
       </c>
       <c r="D6" t="n">
-        <v>49.42903341341842</v>
+        <v>45.08185457901354</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.905032514595317</v>
+        <v>7.066619975168541</v>
       </c>
       <c r="C7" t="n">
-        <v>171.4553643127757</v>
+        <v>217.8674870310437</v>
       </c>
       <c r="D7" t="n">
-        <v>34.73423377625215</v>
+        <v>32.27888276793088</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.005530633326986</v>
+        <v>3.588287859022091</v>
       </c>
       <c r="C8" t="n">
-        <v>111.1534750748239</v>
+        <v>124.0045525234146</v>
       </c>
       <c r="D8" t="n">
-        <v>31.71045084717197</v>
+        <v>30.29182541453534</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.664062358698343</v>
       </c>
       <c r="C9" t="n">
-        <v>38.162496759482</v>
+        <v>36.60937189136354</v>
       </c>
       <c r="D9" t="n">
-        <v>32.39374724932775</v>
+        <v>31.06249736236907</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>26.05067533218912</v>
       </c>
       <c r="D10" t="n">
-        <v>23.48831382410494</v>
+        <v>23.34596040698915</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>20.7904711328347</v>
+        <v>19.19120412261664</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>22.56743447752142</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.83853571261379</v>
+        <v>14.97067074205961</v>
       </c>
       <c r="D12" t="n">
-        <v>20.82875929330033</v>
+        <v>21.26269177857742</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.78864650614645</v>
+        <v>12.74799393964483</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>15.60978849752428</v>
       </c>
     </row>
     <row r="14">
@@ -2820,7 +2820,7 @@
         <v>13.21334235145782</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>14.13520344574558</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.541826921753</v>
+        <v>11.82515109765283</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>12.18348900970292</v>
       </c>
     </row>
     <row r="16">
@@ -2848,7 +2848,7 @@
         <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
-        <v>9.506263020221864</v>
+        <v>8.679631453246051</v>
       </c>
     </row>
     <row r="17">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30.49799243242716</v>
+        <v>28.35778243716912</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>2.675262494072558</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.852377991464484</v>
+        <v>2.630102099677205</v>
       </c>
       <c r="C2" t="n">
-        <v>4.336379609658161</v>
+        <v>9.673160129943822</v>
       </c>
       <c r="D2" t="n">
-        <v>14.3266442480737</v>
+        <v>15.24359660384022</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.74094177926586</v>
+        <v>10.49979169691964</v>
       </c>
       <c r="C3" t="n">
-        <v>16.66516727958961</v>
+        <v>23.49813130114741</v>
       </c>
       <c r="D3" t="n">
-        <v>66.35632733004192</v>
+        <v>74.58828183015142</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.31743297030376</v>
+        <v>32.05995302988384</v>
       </c>
       <c r="C4" t="n">
-        <v>75.44043883743765</v>
+        <v>122.1519946055009</v>
       </c>
       <c r="D4" t="n">
-        <v>130.4605254265416</v>
+        <v>148.7877915694211</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>51.39449231732053</v>
+        <v>42.92691836819179</v>
       </c>
       <c r="C5" t="n">
-        <v>171.8549356284042</v>
+        <v>274.3739396443774</v>
       </c>
       <c r="D5" t="n">
-        <v>117.7851808170111</v>
+        <v>117.8588118948296</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.93593402397926</v>
+        <v>34.77743067523902</v>
       </c>
       <c r="C6" t="n">
-        <v>236.1564650134576</v>
+        <v>309.897498574844</v>
       </c>
       <c r="D6" t="n">
-        <v>65.61019907481435</v>
+        <v>58.64666260859173</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.48689010804419</v>
+        <v>14.55244622005047</v>
       </c>
       <c r="C7" t="n">
-        <v>224.3352409066217</v>
+        <v>266.794847367592</v>
       </c>
       <c r="D7" t="n">
-        <v>39.28561613314036</v>
+        <v>36.35117224514665</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.340707511102648</v>
+        <v>4.589670517353839</v>
       </c>
       <c r="C8" t="n">
-        <v>160.8053652171063</v>
+        <v>186.1737258948439</v>
       </c>
       <c r="D8" t="n">
-        <v>33.62976760897448</v>
+        <v>31.71045084717197</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>1.996874830438012</v>
       </c>
       <c r="C9" t="n">
-        <v>75.77030606606456</v>
+        <v>75.32655610374501</v>
       </c>
       <c r="D9" t="n">
-        <v>33.28124717396686</v>
+        <v>31.72812230584841</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>34.44952694202058</v>
+        <v>31.8871654339364</v>
       </c>
       <c r="D10" t="n">
-        <v>25.0542014123786</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>24.6997904911455</v>
+        <v>22.56743447752142</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>23.45591614986479</v>
       </c>
     </row>
     <row r="12">
@@ -3100,7 +3100,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.22516438163779</v>
+        <v>17.14033316844506</v>
       </c>
       <c r="D12" t="n">
         <v>21.26269177857742</v>
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>16.1301147807751</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>15.60978849752428</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>14.13520344574558</v>
+        <v>13.82791641431633</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>13.82791641431633</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>12.90016483380309</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>11.46681318560274</v>
       </c>
     </row>
     <row r="16">
@@ -3156,10 +3156,10 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>23.97231544229862</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>7.852999886270235</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34.47210713921825</v>
+        <v>33.0554452019901</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>4.249985811684442</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.070104997629023</v>
+        <v>0.5350524988145117</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.502474898125119</v>
+        <v>1.841758693167016</v>
       </c>
       <c r="C2" t="n">
-        <v>2.575124228239384</v>
+        <v>5.017712516405448</v>
       </c>
       <c r="D2" t="n">
-        <v>10.56556879310417</v>
+        <v>11.78980818029994</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.21079801897258</v>
+        <v>9.896016858807849</v>
       </c>
       <c r="C3" t="n">
-        <v>16.93514789825748</v>
+        <v>29.6242369756475</v>
       </c>
       <c r="D3" t="n">
-        <v>63.37672304765285</v>
+        <v>71.5448639469863</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.22059980048183</v>
+        <v>28.12903522207961</v>
       </c>
       <c r="C4" t="n">
-        <v>62.47351515974578</v>
+        <v>100.2639295393183</v>
       </c>
       <c r="D4" t="n">
-        <v>133.3959510622396</v>
+        <v>150.8808776748753</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>56.67138622764714</v>
+        <v>46.19122948481243</v>
       </c>
       <c r="C5" t="n">
-        <v>164.8354395430395</v>
+        <v>263.6728896680871</v>
       </c>
       <c r="D5" t="n">
-        <v>131.7750856025282</v>
+        <v>131.5541923690726</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.10702016642546</v>
+        <v>39.60762938013333</v>
       </c>
       <c r="C6" t="n">
-        <v>260.5087168172997</v>
+        <v>362.1441478994507</v>
       </c>
       <c r="D6" t="n">
-        <v>77.12217265481245</v>
+        <v>69.99762956509335</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.46881773874025</v>
+        <v>12.81573453123786</v>
       </c>
       <c r="C7" t="n">
-        <v>271.9450958240707</v>
+        <v>326.8611171565245</v>
       </c>
       <c r="D7" t="n">
-        <v>43.89688509998763</v>
+        <v>39.88448223273092</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.422773407631881</v>
+        <v>3.67173641388307</v>
       </c>
       <c r="C8" t="n">
-        <v>202.4461940927348</v>
+        <v>229.9842171968578</v>
       </c>
       <c r="D8" t="n">
-        <v>35.549084370777</v>
+        <v>32.12769362147687</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>1.553124868118454</v>
       </c>
       <c r="C9" t="n">
-        <v>89.30467991681108</v>
+        <v>79.5421807457808</v>
       </c>
       <c r="D9" t="n">
-        <v>33.05937219280708</v>
+        <v>31.39530983410874</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>34.87658719336794</v>
+        <v>31.74481201682062</v>
       </c>
       <c r="D10" t="n">
-        <v>25.48126166372597</v>
+        <v>24.62714116103124</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>22.0343454741154</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>23.63361248433346</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.7912318963607</v>
+        <v>15.62156946997525</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>19.7439280801076</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.70734137314322</v>
+        <v>11.44717823151781</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>15.60978849752428</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>10.75504610002381</v>
       </c>
       <c r="D14" t="n">
-        <v>11.36962016288231</v>
+        <v>10.75504610002381</v>
       </c>
     </row>
     <row r="15">
@@ -3453,10 +3453,10 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>20.0669230748048</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>6.450082416901544</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>28.10547327717769</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0.4722206457427158</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.314380249537232</v>
+        <v>2.39153740754523</v>
       </c>
       <c r="C2" t="n">
-        <v>6.42062998577414</v>
+        <v>5.805074175211389</v>
       </c>
       <c r="D2" t="n">
-        <v>11.38925511696725</v>
+        <v>13.8357703959503</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.42754327743287</v>
+        <v>8.153414683769761</v>
       </c>
       <c r="C3" t="n">
-        <v>13.67574552015807</v>
+        <v>25.00511402716626</v>
       </c>
       <c r="D3" t="n">
-        <v>58.47289326494003</v>
+        <v>65.66910393706915</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.702596865538</v>
+        <v>23.76418492899829</v>
       </c>
       <c r="C4" t="n">
-        <v>52.59516975961437</v>
+        <v>89.01997308257953</v>
       </c>
       <c r="D4" t="n">
-        <v>132.5791369723063</v>
+        <v>151.0085048764274</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>56.3768619163731</v>
+        <v>45.01313223971626</v>
       </c>
       <c r="C5" t="n">
-        <v>142.5252229640307</v>
+        <v>231.643370817035</v>
       </c>
       <c r="D5" t="n">
-        <v>145.7159030028328</v>
+        <v>147.3357867148401</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>59.69320566131882</v>
+        <v>46.65166915810419</v>
       </c>
       <c r="C6" t="n">
-        <v>264.6948890282081</v>
+        <v>384.2825586302163</v>
       </c>
       <c r="D6" t="n">
-        <v>94.79264958355078</v>
+        <v>85.89703363537045</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>30.78171751895449</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="C7" t="n">
-        <v>316.0216407539355</v>
+        <v>399.3838018169407</v>
       </c>
       <c r="D7" t="n">
-        <v>52.46067032413256</v>
+        <v>46.35223610830891</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.595201150680824</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>268.2871038780471</v>
+        <v>305.0044680168778</v>
       </c>
       <c r="D8" t="n">
-        <v>38.13598957146735</v>
+        <v>34.04701038327938</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.551562283337459</v>
+        <v>1.996874830438012</v>
       </c>
       <c r="C9" t="n">
-        <v>149.0999873393716</v>
+        <v>146.7703000371938</v>
       </c>
       <c r="D9" t="n">
-        <v>34.16874709860598</v>
+        <v>32.06093477758807</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7117670855789376</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>60.50020227420969</v>
+        <v>50.53546307610457</v>
       </c>
       <c r="D10" t="n">
-        <v>27.04714925199963</v>
+        <v>25.48126166372597</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>29.67528785626833</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>21.04572553593887</v>
+        <v>18.22516438163779</v>
       </c>
       <c r="D12" t="n">
-        <v>20.39482680802324</v>
+        <v>19.96089432274615</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.78864650614645</v>
+        <v>12.74799393964483</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.98419422574081</v>
+        <v>11.36962016288231</v>
       </c>
       <c r="D14" t="n">
-        <v>11.67690719431156</v>
+        <v>10.75504610002381</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>6.091744504851459</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>2.89321048441535</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.022220344299182</v>
+        <v>4.5553093477052</v>
       </c>
       <c r="C2" t="n">
-        <v>11.84674954714626</v>
+        <v>16.22534430808703</v>
       </c>
       <c r="D2" t="n">
-        <v>12.12065715663112</v>
+        <v>5.89735845941059</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.34539526544563</v>
+        <v>1.764200624531518</v>
       </c>
       <c r="C2" t="n">
-        <v>3.595160092951819</v>
+        <v>3.483240854667684</v>
       </c>
       <c r="D2" t="n">
-        <v>8.382161898859268</v>
+        <v>10.4045621696077</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.06491852166731</v>
+        <v>10.90230825566083</v>
       </c>
       <c r="C3" t="n">
-        <v>19.25698121880119</v>
+        <v>28.78484268851648</v>
       </c>
       <c r="D3" t="n">
-        <v>63.20491719940965</v>
+        <v>70.82327938436491</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.29114676646735</v>
+        <v>33.56595400819845</v>
       </c>
       <c r="C4" t="n">
-        <v>76.64013453202725</v>
+        <v>129.74581309785</v>
       </c>
       <c r="D4" t="n">
-        <v>135.8208678917292</v>
+        <v>152.4889804144316</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.71107274197773</v>
+        <v>26.26175108860219</v>
       </c>
       <c r="C5" t="n">
-        <v>219.3469808213437</v>
+        <v>332.9106465100934</v>
       </c>
       <c r="D5" t="n">
-        <v>134.6221539448439</v>
+        <v>130.8424252834937</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>19.07928488433252</v>
+        <v>14.41009280293469</v>
       </c>
       <c r="C6" t="n">
-        <v>262.6018029227538</v>
+        <v>327.0849556330929</v>
       </c>
       <c r="D6" t="n">
-        <v>76.15613291383359</v>
+        <v>68.10580173900973</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.689227946110266</v>
+        <v>4.311835917051991</v>
       </c>
       <c r="C7" t="n">
-        <v>188.6428213710246</v>
+        <v>214.4539502633775</v>
       </c>
       <c r="D7" t="n">
-        <v>34.01559445674349</v>
+        <v>29.34443887993716</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.752419652080557</v>
+        <v>1.335176877775662</v>
       </c>
       <c r="C8" t="n">
-        <v>109.9017467519092</v>
+        <v>108.1493270998286</v>
       </c>
       <c r="D8" t="n">
-        <v>25.11801501315464</v>
+        <v>23.61594102565702</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4437499623195582</v>
+        <v>0.2218749811597791</v>
       </c>
       <c r="C9" t="n">
-        <v>46.14999608123405</v>
+        <v>38.49530923122167</v>
       </c>
       <c r="D9" t="n">
-        <v>20.63437324785945</v>
+        <v>19.41406085148067</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>23.20360698987336</v>
+        <v>20.64124548178919</v>
       </c>
       <c r="D10" t="n">
-        <v>19.07535789351553</v>
+        <v>18.79065105928395</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>16.8811517745239</v>
+        <v>14.57109942643116</v>
       </c>
       <c r="D11" t="n">
-        <v>16.34806277111788</v>
+        <v>15.99267010218054</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>11.0652783745658</v>
+        <v>10.41437964665016</v>
       </c>
       <c r="D12" t="n">
-        <v>13.4519070435898</v>
+        <v>12.80100831567416</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.886199381765381</v>
+        <v>9.365873098514571</v>
       </c>
       <c r="D13" t="n">
-        <v>9.626036240139976</v>
+        <v>8.845546815263763</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>16.90078672860884</v>
+        <v>17.8226478228966</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>4.916592502868027</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>21.85861263505523</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>2.150027472300515</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.695118432335748</v>
+        <v>6.574764375340889</v>
       </c>
       <c r="C2" t="n">
-        <v>5.273948667213865</v>
+        <v>8.51666133434108</v>
       </c>
       <c r="D2" t="n">
-        <v>12.1746532803647</v>
+        <v>6.300856765856029</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>8.551022503989719</v>
+        <v>9.680032363873551</v>
       </c>
       <c r="C3" t="n">
-        <v>29.85003894762427</v>
+        <v>40.88488314335842</v>
       </c>
       <c r="D3" t="n">
-        <v>13.31740760810798</v>
+        <v>8.089601082993717</v>
       </c>
     </row>
     <row r="4">
@@ -4557,7 +4557,7 @@
         <v>4.736932672990861</v>
       </c>
       <c r="C5" t="n">
-        <v>9.449321653375552</v>
+        <v>9.35114688295087</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4571,7 +4571,7 @@
         <v>8.050331174823848</v>
       </c>
       <c r="C6" t="n">
-        <v>18.27425176685013</v>
+        <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
         <v>32.8453511932813</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39719771873956</v>
+        <v>13.39742247980036</v>
       </c>
       <c r="C21" t="n">
-        <v>70.13827040987184</v>
+        <v>70.13944710013129</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576140908087007</v>
+        <v>1.576167350564748</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.104687151455915</v>
+        <v>4.703553251046468</v>
       </c>
       <c r="C2" t="n">
-        <v>3.082687791334985</v>
+        <v>8.203483816686347</v>
       </c>
       <c r="D2" t="n">
-        <v>14.04488265695487</v>
+        <v>19.63495408493621</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.18763698469816</v>
+        <v>17.45056544298705</v>
       </c>
       <c r="C3" t="n">
-        <v>24.04300127700439</v>
+        <v>36.08413686959152</v>
       </c>
       <c r="D3" t="n">
-        <v>20.32217747790898</v>
+        <v>11.42754327743287</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>10.09531164276995</v>
+        <v>11.37158365829081</v>
       </c>
       <c r="C4" t="n">
-        <v>46.03513159983719</v>
+        <v>62.83087132409162</v>
       </c>
       <c r="D4" t="n">
-        <v>22.05398042820035</v>
+        <v>19.30999559483051</v>
       </c>
     </row>
     <row r="5">
@@ -4868,7 +4868,7 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.424156065963628</v>
+        <v>5.473243451175969</v>
       </c>
       <c r="D5" t="n">
         <v>29.40334374219198</v>
@@ -4882,7 +4882,7 @@
         <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.50317890838889</v>
+        <v>16.34217228489241</v>
       </c>
       <c r="D6" t="n">
         <v>34.57617239586842</v>
@@ -4896,7 +4896,7 @@
         <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.3139636433765</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
         <v>34.97378021608837</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5025,7 +5025,7 @@
         <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>31.63878326476196</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>36.36098972218912</v>
       </c>
     </row>
     <row r="18">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43910185837896</v>
+        <v>15.43835584477201</v>
       </c>
       <c r="C21" t="n">
-        <v>86.1339366835879</v>
+        <v>86.1297747129386</v>
       </c>
       <c r="D21" t="n">
-        <v>3.25033723334294</v>
+        <v>3.250180177846739</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.371722527011046</v>
+        <v>4.494440990041897</v>
       </c>
       <c r="C2" t="n">
-        <v>4.513094196422587</v>
+        <v>6.039711876526377</v>
       </c>
       <c r="D2" t="n">
-        <v>20.42427923915064</v>
+        <v>27.68430351205581</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.64276700884118</v>
+        <v>16.75843331149305</v>
       </c>
       <c r="C3" t="n">
-        <v>16.73388961888688</v>
+        <v>33.58068022376215</v>
       </c>
       <c r="D3" t="n">
-        <v>26.84098223410779</v>
+        <v>24.47987900539422</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.03296281578367</v>
+        <v>23.68760860806704</v>
       </c>
       <c r="C4" t="n">
-        <v>54.40747602165398</v>
+        <v>78.77150879794708</v>
       </c>
       <c r="D4" t="n">
-        <v>27.28669569183585</v>
+        <v>20.71389481190345</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>9.302059497738529</v>
+        <v>10.30835089459151</v>
       </c>
       <c r="C5" t="n">
-        <v>50.78090000216628</v>
+        <v>67.29880512611886</v>
       </c>
       <c r="D5" t="n">
-        <v>30.58144098728815</v>
+        <v>29.91876128692155</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.957245069369646</v>
+        <v>5.916993413495527</v>
       </c>
       <c r="C6" t="n">
-        <v>12.11574841810989</v>
+        <v>12.23650338573225</v>
       </c>
       <c r="D6" t="n">
-        <v>36.54850353370026</v>
+        <v>36.10573531908495</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.521970983489814</v>
       </c>
       <c r="C7" t="n">
         <v>24.37385025333556</v>
       </c>
       <c r="D7" t="n">
-        <v>37.12969817461437</v>
+        <v>37.4890178343687</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>10.34762080276138</v>
       </c>
       <c r="C8" t="n">
         <v>29.79113408536946</v>
       </c>
       <c r="D8" t="n">
-        <v>38.38633523605029</v>
+        <v>37.88564390688441</v>
       </c>
     </row>
     <row r="9">
@@ -5232,10 +5232,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>29.39843500367073</v>
       </c>
       <c r="D9" t="n">
         <v>41.15780900513902</v>
@@ -5249,7 +5249,7 @@
         <v>9.395325529641976</v>
       </c>
       <c r="C10" t="n">
-        <v>29.60951076008381</v>
+        <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5260,7 +5260,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.174031385558941</v>
+        <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
         <v>31.27455486648638</v>
@@ -5277,7 +5277,7 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>31.89403766786613</v>
+        <v>31.67707142522758</v>
       </c>
       <c r="D12" t="n">
         <v>46.2138096820101</v>
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>27.23368131580652</v>
+        <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>43.71722527011046</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5333,7 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
         <v>40.91826256530281</v>
@@ -5350,7 +5350,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73183507276176</v>
+        <v>16.72483000168812</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0641939438467</v>
+        <v>102.0214630102975</v>
       </c>
       <c r="D21" t="n">
-        <v>5.019550521828528</v>
+        <v>4.181207500422031</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.676064315327558</v>
+        <v>4.340306600475149</v>
       </c>
       <c r="C2" t="n">
-        <v>7.39943244690821</v>
+        <v>7.352308557104362</v>
       </c>
       <c r="D2" t="n">
-        <v>19.75767254796706</v>
+        <v>34.29539255245383</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.82929907264807</v>
+        <v>15.97794388661684</v>
       </c>
       <c r="C3" t="n">
-        <v>17.17567608579795</v>
+        <v>27.7932775072272</v>
       </c>
       <c r="D3" t="n">
-        <v>36.39338739642926</v>
+        <v>40.0749412873548</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.09150782513998</v>
+        <v>28.37152690502857</v>
       </c>
       <c r="C4" t="n">
-        <v>47.41350537659971</v>
+        <v>81.63035811271379</v>
       </c>
       <c r="D4" t="n">
-        <v>34.20409001595887</v>
+        <v>27.91206897944107</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>20.29763378530281</v>
+        <v>22.48202242725196</v>
       </c>
       <c r="C5" t="n">
-        <v>77.14082586119314</v>
+        <v>108.7285582453343</v>
       </c>
       <c r="D5" t="n">
-        <v>33.13398501832986</v>
+        <v>30.704159450319</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>9.378635818669782</v>
+        <v>9.94215900090745</v>
       </c>
       <c r="C6" t="n">
-        <v>48.18123208132072</v>
+        <v>60.01521890831177</v>
       </c>
       <c r="D6" t="n">
-        <v>38.35982804803563</v>
+        <v>37.35353665118265</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>8.563785224144926</v>
       </c>
       <c r="C7" t="n">
-        <v>21.13997331554657</v>
+        <v>21.31963314542373</v>
       </c>
       <c r="D7" t="n">
-        <v>39.22572952318131</v>
+        <v>39.76470901281281</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>10.76486357706628</v>
       </c>
       <c r="C8" t="n">
-        <v>31.46010518258904</v>
+        <v>31.37665662772806</v>
       </c>
       <c r="D8" t="n">
-        <v>40.13875488813084</v>
+        <v>39.30426933952106</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>10.6499990956694</v>
       </c>
       <c r="C9" t="n">
-        <v>34.27968458918587</v>
+        <v>34.05780960802609</v>
       </c>
       <c r="D9" t="n">
-        <v>41.82343394861835</v>
+        <v>42.15624642035802</v>
       </c>
     </row>
     <row r="10">
@@ -5563,7 +5563,7 @@
         <v>33.31069960509428</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>48.68486865359933</v>
       </c>
     </row>
     <row r="11">
@@ -5571,7 +5571,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.707120388964958</v>
+        <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
         <v>33.40691088011046</v>
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>7.159886007071988</v>
       </c>
       <c r="C12" t="n">
-        <v>34.49763257952867</v>
+        <v>34.28066633689012</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>47.73257338047992</v>
       </c>
     </row>
     <row r="13">
@@ -5602,10 +5602,10 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>33.04071898642641</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="14">
@@ -5619,7 +5619,7 @@
         <v>30.42141611149592</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>45.7857676829585</v>
       </c>
     </row>
     <row r="15">
@@ -5630,7 +5630,7 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.02537087605695</v>
+        <v>29.38370878810703</v>
       </c>
       <c r="D15" t="n">
         <v>43.71722527011046</v>
@@ -5661,7 +5661,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5689,7 +5689,7 @@
         <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>25.27607639353838</v>
       </c>
     </row>
     <row r="20">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.05674155266553</v>
+        <v>18.03685049348418</v>
       </c>
       <c r="C21" t="n">
-        <v>117.7987425102465</v>
+        <v>117.6689770289206</v>
       </c>
       <c r="D21" t="n">
-        <v>6.878758686729725</v>
+        <v>6.01228349782806</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.175193059712438</v>
+        <v>7.141232800691299</v>
       </c>
       <c r="C2" t="n">
-        <v>6.94390151213769</v>
+        <v>5.977861771158828</v>
       </c>
       <c r="D2" t="n">
-        <v>22.60179564717007</v>
+        <v>27.81094896590364</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.79355524466769</v>
+        <v>13.59720570381833</v>
       </c>
       <c r="C3" t="n">
-        <v>22.36421270274234</v>
+        <v>26.41392198276044</v>
       </c>
       <c r="D3" t="n">
-        <v>40.74743846476387</v>
+        <v>52.82784396552087</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>19.61630087855552</v>
+        <v>21.58175978245763</v>
       </c>
       <c r="C4" t="n">
-        <v>37.58621085708914</v>
+        <v>62.00129451400306</v>
       </c>
       <c r="D4" t="n">
-        <v>38.53065214857457</v>
+        <v>34.85498874387451</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>17.89235190989812</v>
+        <v>19.61041039233004</v>
       </c>
       <c r="C5" t="n">
-        <v>60.96653243372694</v>
+        <v>97.11939164261574</v>
       </c>
       <c r="D5" t="n">
-        <v>30.33600406122645</v>
+        <v>27.3171298706675</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.02266231265569</v>
+        <v>10.82769543013807</v>
       </c>
       <c r="C6" t="n">
-        <v>59.04917916733292</v>
+        <v>78.93349716914781</v>
       </c>
       <c r="D6" t="n">
-        <v>31.23528495831652</v>
+        <v>29.7057220351</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4.970588626601601</v>
+        <v>5.150248456478767</v>
       </c>
       <c r="C7" t="n">
-        <v>29.10489244010094</v>
+        <v>33.77604801690726</v>
       </c>
       <c r="D7" t="n">
-        <v>30.60205768907732</v>
+        <v>31.02126395879071</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>4.756567627075796</v>
       </c>
       <c r="C8" t="n">
         <v>18.60902773399829</v>
       </c>
       <c r="D8" t="n">
-        <v>30.12492830481337</v>
+        <v>29.37389131106456</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>4.77031209493525</v>
       </c>
       <c r="C9" t="n">
-        <v>21.85468564423824</v>
+        <v>21.63281066307846</v>
       </c>
       <c r="D9" t="n">
-        <v>29.84218496599028</v>
+        <v>30.17499743772996</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>21.49536598448391</v>
+        <v>21.35301256736813</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>33.16834618797849</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>20.07968579496001</v>
       </c>
       <c r="D11" t="n">
-        <v>34.47308888692249</v>
+        <v>34.65078522139116</v>
       </c>
     </row>
     <row r="12">
@@ -5899,7 +5899,7 @@
         <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
         <v>32.11100391050467</v>
@@ -5910,10 +5910,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>2.081305133003238</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
         <v>30.17892442854696</v>
@@ -5944,7 +5944,7 @@
         <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>27.95035713990669</v>
       </c>
     </row>
     <row r="16">
@@ -5958,7 +5958,7 @@
         <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -5972,7 +5972,7 @@
         <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>23.13881164139307</v>
       </c>
     </row>
     <row r="18">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.057492497875534</v>
+        <v>7.04220247504499</v>
       </c>
       <c r="C21" t="n">
-        <v>66.16399216758313</v>
+        <v>66.02064820354678</v>
       </c>
       <c r="D21" t="n">
-        <v>5.293119373406651</v>
+        <v>4.401376546903119</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.585162689460105</v>
+        <v>4.821362975556085</v>
       </c>
       <c r="C2" t="n">
-        <v>5.375068680751286</v>
+        <v>5.734388340505619</v>
       </c>
       <c r="D2" t="n">
-        <v>20.00801821255</v>
+        <v>26.46399111567702</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.61393647251952</v>
+        <v>20.24363766156923</v>
       </c>
       <c r="C3" t="n">
-        <v>25.5008966178109</v>
+        <v>24.71058971589222</v>
       </c>
       <c r="D3" t="n">
-        <v>50.39801839751001</v>
+        <v>63.42581043286518</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.3767954964483</v>
+        <v>24.54271085846601</v>
       </c>
       <c r="C4" t="n">
-        <v>49.43001516112266</v>
+        <v>64.01780429852602</v>
       </c>
       <c r="D4" t="n">
-        <v>51.5869148673529</v>
+        <v>54.45852690227482</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>24.64186737659495</v>
+        <v>27.09623663721197</v>
       </c>
       <c r="C5" t="n">
-        <v>66.41523219229673</v>
+        <v>107.820441618906</v>
       </c>
       <c r="D5" t="n">
-        <v>38.2145293878071</v>
+        <v>33.84575210390879</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>18.35475507859837</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="C6" t="n">
-        <v>81.87186804795851</v>
+        <v>122.6870471043154</v>
       </c>
       <c r="D6" t="n">
-        <v>34.01264921363075</v>
+        <v>32.16107304342126</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.042878103817369</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>62.46173418729481</v>
+        <v>79.64919124554372</v>
       </c>
       <c r="D7" t="n">
-        <v>33.35684174719388</v>
+        <v>33.11729530735765</v>
       </c>
     </row>
     <row r="8">
@@ -6154,10 +6154,10 @@
         <v>5.424156065963627</v>
       </c>
       <c r="C8" t="n">
-        <v>30.62561963397925</v>
+        <v>33.62976760897448</v>
       </c>
       <c r="D8" t="n">
-        <v>32.12769362147687</v>
+        <v>31.2097595180061</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>4.992187076095029</v>
       </c>
       <c r="C9" t="n">
-        <v>23.2968730217768</v>
+        <v>23.18593553119691</v>
       </c>
       <c r="D9" t="n">
-        <v>30.95155987178918</v>
+        <v>31.39530983410874</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.840016181936776</v>
+        <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>24.76949457814703</v>
+        <v>24.20008090968388</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>33.73775985644164</v>
       </c>
     </row>
     <row r="11">
@@ -6199,7 +6199,7 @@
         <v>23.10052348092744</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>35.00617789032851</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>22.1305567491316</v>
+        <v>21.91359050649305</v>
       </c>
       <c r="D12" t="n">
-        <v>32.97886888105885</v>
+        <v>33.1958351236974</v>
       </c>
     </row>
     <row r="13">
@@ -6221,7 +6221,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
         <v>21.07321447165778</v>
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -6252,7 +6252,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -6283,7 +6283,7 @@
         <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -6311,7 +6311,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.281488251645532</v>
+        <v>7.256862183898595</v>
       </c>
       <c r="C21" t="n">
-        <v>75.54544061082241</v>
+        <v>75.28994515794793</v>
       </c>
       <c r="D21" t="n">
-        <v>6.371302220189841</v>
+        <v>5.442646637923946</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.028110830524663</v>
+        <v>4.243113577754714</v>
       </c>
       <c r="C2" t="n">
-        <v>5.728497854280139</v>
+        <v>12.42205370183489</v>
       </c>
       <c r="D2" t="n">
-        <v>17.27188736081413</v>
+        <v>30.25059201095697</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.09499284760046</v>
+        <v>18.20160243673586</v>
       </c>
       <c r="C3" t="n">
-        <v>22.68818944514379</v>
+        <v>23.27232932917064</v>
       </c>
       <c r="D3" t="n">
-        <v>54.70789081915351</v>
+        <v>69.42919764433444</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.4090543019682</v>
+        <v>32.36625831360885</v>
       </c>
       <c r="C4" t="n">
-        <v>58.10866486666446</v>
+        <v>62.8053458837812</v>
       </c>
       <c r="D4" t="n">
-        <v>64.77080478768332</v>
+        <v>72.41567416065323</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.21957699504858</v>
+        <v>32.49584901056943</v>
       </c>
       <c r="C5" t="n">
-        <v>80.9696419077557</v>
+        <v>113.6372967665683</v>
       </c>
       <c r="D5" t="n">
-        <v>48.74377351585415</v>
+        <v>45.7248993252952</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>26.84785446803753</v>
+        <v>28.37741739125406</v>
       </c>
       <c r="C6" t="n">
-        <v>95.4366760775367</v>
+        <v>147.6430737462694</v>
       </c>
       <c r="D6" t="n">
-        <v>38.76234460677682</v>
+        <v>35.74347041621788</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.10949807898591</v>
+        <v>16.76825078853552</v>
       </c>
       <c r="C7" t="n">
-        <v>93.84231780583987</v>
+        <v>131.9900883497582</v>
       </c>
       <c r="D7" t="n">
-        <v>35.69241953559704</v>
+        <v>34.85400699617026</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.844164156932015</v>
+        <v>7.927612711792993</v>
       </c>
       <c r="C8" t="n">
-        <v>58.99812828671206</v>
+        <v>71.5154115158589</v>
       </c>
       <c r="D8" t="n">
-        <v>34.29735604786232</v>
+        <v>33.37942194439155</v>
       </c>
     </row>
     <row r="9">
@@ -6476,10 +6476,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>5.435937038414587</v>
       </c>
       <c r="C9" t="n">
-        <v>31.94999728700819</v>
+        <v>33.05937219280708</v>
       </c>
       <c r="D9" t="n">
         <v>32.28280975874785</v>
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>4.982369599052563</v>
       </c>
       <c r="C10" t="n">
-        <v>27.18950266911542</v>
+        <v>26.62008900065227</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>34.30717352490479</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.65445017030089</v>
+        <v>26.12136116689488</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>35.18387422479719</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>24.30021917551705</v>
       </c>
       <c r="D12" t="n">
-        <v>33.62976760897449</v>
+        <v>34.06370009425158</v>
       </c>
     </row>
     <row r="13">
@@ -6532,10 +6532,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>23.41468274628643</v>
+        <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
         <v>31.73990327829938</v>
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
         <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>19.35024725070463</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -6577,10 +6577,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>17.3592629064921</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -6608,7 +6608,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.493801569829611</v>
+        <v>7.457430421742454</v>
       </c>
       <c r="C21" t="n">
-        <v>85.24199285681182</v>
+        <v>83.89609224460261</v>
       </c>
       <c r="D21" t="n">
-        <v>7.493801569829611</v>
+        <v>6.525251619024647</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_6_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_6_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497631369879</v>
+        <v>10.84497626885457</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907187738996</v>
+        <v>37.78907172113131</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.119413367019616</v>
+        <v>5.984734005088556</v>
       </c>
       <c r="C2" t="n">
-        <v>17.71760081854219</v>
+        <v>13.74250436404685</v>
       </c>
       <c r="D2" t="n">
-        <v>29.00573592197201</v>
+        <v>24.2550587811217</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.13502351929633</v>
+        <v>19.46314823669302</v>
       </c>
       <c r="C3" t="n">
-        <v>36.56028450615122</v>
+        <v>24.33752558827843</v>
       </c>
       <c r="D3" t="n">
-        <v>76.43396751413542</v>
+        <v>69.74335690969342</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.32346232524949</v>
+        <v>40.76412817573606</v>
       </c>
       <c r="C4" t="n">
-        <v>60.34214089382595</v>
+        <v>51.71454206890498</v>
       </c>
       <c r="D4" t="n">
-        <v>88.89234588102745</v>
+        <v>86.19941192827845</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.98167525545136</v>
+        <v>50.9281621578033</v>
       </c>
       <c r="C5" t="n">
-        <v>113.588209381356</v>
+        <v>83.76762286485911</v>
       </c>
       <c r="D5" t="n">
-        <v>59.15029918087033</v>
+        <v>64.32901832077226</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.14598697495907</v>
+        <v>48.06047711369836</v>
       </c>
       <c r="C6" t="n">
-        <v>164.3475109340288</v>
+        <v>96.24170919501908</v>
       </c>
       <c r="D6" t="n">
-        <v>41.66046382971341</v>
+        <v>46.85292743747478</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.79305652304895</v>
+        <v>35.27321326588365</v>
       </c>
       <c r="C7" t="n">
-        <v>170.9762714331032</v>
+        <v>84.20057360243193</v>
       </c>
       <c r="D7" t="n">
-        <v>37.36924461445059</v>
+        <v>39.1059563032632</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.85107744859075</v>
+        <v>19.02627050830318</v>
       </c>
       <c r="C8" t="n">
-        <v>122.0852357616121</v>
+        <v>56.57812019574367</v>
       </c>
       <c r="D8" t="n">
-        <v>34.88149593188918</v>
+        <v>36.80081269369168</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.767186925373262</v>
+        <v>8.764061755811273</v>
       </c>
       <c r="C9" t="n">
-        <v>59.46249495082079</v>
+        <v>35.38905949498476</v>
       </c>
       <c r="D9" t="n">
-        <v>33.72499713628642</v>
+        <v>34.27968458918587</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.267076433284139</v>
+        <v>5.694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>33.16834618797849</v>
+        <v>30.17892442854695</v>
       </c>
       <c r="D10" t="n">
-        <v>34.59188035913637</v>
+        <v>35.01894061048373</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>28.96450251839364</v>
+        <v>29.852984190737</v>
       </c>
       <c r="D11" t="n">
-        <v>35.7169632282032</v>
+        <v>36.42774856607789</v>
       </c>
     </row>
     <row r="12">
@@ -923,7 +923,7 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>26.90381408717959</v>
+        <v>27.98864530037232</v>
       </c>
       <c r="D12" t="n">
         <v>34.49763257952867</v>
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.23582473766426</v>
+        <v>26.27647730416588</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>32.780555844801</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>23.96838845148163</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -962,13 +962,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
         <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>18.59921025695582</v>
+        <v>19.01252604044373</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -993,10 +993,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1007,10 +1007,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -1024,7 +1024,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.642201151489</v>
+        <v>7.705614607394949</v>
       </c>
       <c r="C21" t="n">
-        <v>92.66168896180412</v>
+        <v>95.35698076651251</v>
       </c>
       <c r="D21" t="n">
-        <v>7.642201151489</v>
+        <v>8.668816433319318</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.259222451650163</v>
+        <v>9.188176764045899</v>
       </c>
       <c r="C2" t="n">
-        <v>18.9762013753866</v>
+        <v>8.317366550378978</v>
       </c>
       <c r="D2" t="n">
-        <v>28.52762479000382</v>
+        <v>28.89872542220911</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.80966411856313</v>
+        <v>19.74294633240336</v>
       </c>
       <c r="C3" t="n">
-        <v>51.9099098620501</v>
+        <v>40.0307626406637</v>
       </c>
       <c r="D3" t="n">
-        <v>80.19896995992195</v>
+        <v>72.06028149171588</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.53668150352029</v>
+        <v>39.0283982346277</v>
       </c>
       <c r="C4" t="n">
-        <v>74.16416682191679</v>
+        <v>55.79861251857172</v>
       </c>
       <c r="D4" t="n">
-        <v>102.20386300291</v>
+        <v>98.27294519510572</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.00684084286328</v>
+        <v>55.61600744558182</v>
       </c>
       <c r="C5" t="n">
-        <v>112.287393673229</v>
+        <v>89.53539062730911</v>
       </c>
       <c r="D5" t="n">
-        <v>74.51465075233293</v>
+        <v>78.9079717288374</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>43.75354993516761</v>
+        <v>57.92213280285758</v>
       </c>
       <c r="C6" t="n">
-        <v>170.465762626895</v>
+        <v>113.2681596297715</v>
       </c>
       <c r="D6" t="n">
-        <v>48.66425195181016</v>
+        <v>54.74225198880216</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>32.99752208743954</v>
+        <v>46.29234949834984</v>
       </c>
       <c r="C7" t="n">
-        <v>201.8777621719759</v>
+        <v>111.329207913884</v>
       </c>
       <c r="D7" t="n">
-        <v>40.60312155223958</v>
+        <v>43.47767883027424</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>18.77592484372025</v>
+        <v>28.03871443328891</v>
       </c>
       <c r="C8" t="n">
-        <v>167.4812496059846</v>
+        <v>82.78096642209104</v>
       </c>
       <c r="D8" t="n">
-        <v>36.46701847424777</v>
+        <v>38.63668090063322</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>13.64531134132641</v>
       </c>
       <c r="C9" t="n">
-        <v>99.06717908784135</v>
+        <v>52.47343304428775</v>
       </c>
       <c r="D9" t="n">
-        <v>35.05624702324509</v>
+        <v>36.0546844384641</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.836490101747287</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>49.53898915629405</v>
+        <v>36.01541453029424</v>
       </c>
       <c r="D10" t="n">
-        <v>34.87658719336794</v>
+        <v>35.44600086183109</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
-        <v>33.05151821117311</v>
+        <v>32.87382187670443</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>36.96083756948391</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>29.72437524148068</v>
+        <v>30.8092064546734</v>
       </c>
       <c r="D12" t="n">
-        <v>34.71459882216721</v>
+        <v>34.93156506480576</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>27.3171298706675</v>
+        <v>28.87810872041993</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>33.30088212805181</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>24.89024954576939</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -1273,13 +1273,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.57528845915541</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>29.74204670015712</v>
       </c>
     </row>
     <row r="16">
@@ -1287,13 +1287,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.8266315669758143</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.83915760741954</v>
+        <v>20.66578917439536</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>27.69215749368978</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>18.88882582970863</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1318,10 +1318,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -1335,7 +1335,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.810281236258569</v>
+        <v>7.89268562860129</v>
       </c>
       <c r="C21" t="n">
-        <v>100.5573709168291</v>
+        <v>104.5780845789671</v>
       </c>
       <c r="D21" t="n">
-        <v>8.78656639079089</v>
+        <v>9.865857035751612</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.08192702780899</v>
+        <v>9.629963230956964</v>
       </c>
       <c r="C2" t="n">
-        <v>14.09691528527995</v>
+        <v>7.127488332831843</v>
       </c>
       <c r="D2" t="n">
-        <v>28.61696383109027</v>
+        <v>30.19070540099791</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.56070111231194</v>
+        <v>24.5927799913826</v>
       </c>
       <c r="C3" t="n">
-        <v>61.5408548407113</v>
+        <v>36.00068831473054</v>
       </c>
       <c r="D3" t="n">
-        <v>83.32583639794802</v>
+        <v>76.60086462385738</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.21386643527233</v>
+        <v>37.66278717802039</v>
       </c>
       <c r="C4" t="n">
-        <v>96.42235077260048</v>
+        <v>75.87437132271475</v>
       </c>
       <c r="D4" t="n">
-        <v>112.4012764069216</v>
+        <v>108.023663393685</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.79223900626073</v>
+        <v>56.67138622764714</v>
       </c>
       <c r="C5" t="n">
-        <v>120.80405500757</v>
+        <v>95.49950793060849</v>
       </c>
       <c r="D5" t="n">
-        <v>87.91550691530188</v>
+        <v>93.41329405908402</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.46928506929254</v>
+        <v>65.9322123218073</v>
       </c>
       <c r="C6" t="n">
-        <v>172.5991003882233</v>
+        <v>125.2631530802591</v>
       </c>
       <c r="D6" t="n">
-        <v>57.88188114698346</v>
+        <v>64.20139111922018</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>40.24380189248525</v>
+        <v>56.05386692167588</v>
       </c>
       <c r="C7" t="n">
-        <v>221.520570238546</v>
+        <v>135.3437385074653</v>
       </c>
       <c r="D7" t="n">
-        <v>43.83699849002857</v>
+        <v>48.56804067679396</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>25.2849121228766</v>
+        <v>37.55184968744049</v>
       </c>
       <c r="C8" t="n">
-        <v>207.0358646100886</v>
+        <v>110.9865779651019</v>
       </c>
       <c r="D8" t="n">
-        <v>38.63668090063322</v>
+        <v>40.80634332701867</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>13.09062388842696</v>
+        <v>19.85781081380023</v>
       </c>
       <c r="C9" t="n">
-        <v>141.5562379799391</v>
+        <v>74.43905617910588</v>
       </c>
       <c r="D9" t="n">
-        <v>35.83280945730432</v>
+        <v>37.71874679716245</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.117670855789377</v>
+        <v>9.680032363873552</v>
       </c>
       <c r="C10" t="n">
-        <v>75.58966448848317</v>
+        <v>47.83074815090461</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>36.01541453029424</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>5.686282702997524</v>
       </c>
       <c r="C11" t="n">
-        <v>42.46942393801276</v>
+        <v>36.78314123501524</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>37.49392657288993</v>
       </c>
     </row>
     <row r="12">
@@ -1542,10 +1542,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>32.54493639578176</v>
+        <v>34.06370009425158</v>
       </c>
       <c r="D12" t="n">
         <v>35.36549755008285</v>
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>29.39843500367074</v>
+        <v>31.21957699504857</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>33.82120841130262</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>27.04125876577415</v>
+        <v>28.88498095434966</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>24.00864010735575</v>
+        <v>25.083653843506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>30.10038461220721</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.8266315669758143</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.07910495788326</v>
+        <v>21.90573652485908</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>27.69215749368978</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>19.83326712119407</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1629,10 +1629,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>19.25796296650543</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.961247375100001</v>
+        <v>8.064112761277173</v>
       </c>
       <c r="C21" t="n">
-        <v>107.47683956385</v>
+        <v>112.8975786578804</v>
       </c>
       <c r="D21" t="n">
-        <v>9.951559218875001</v>
+        <v>11.08815504675611</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.613633372883262</v>
+        <v>8.720864856824416</v>
       </c>
       <c r="C2" t="n">
-        <v>9.92350579452676</v>
+        <v>4.788965301315941</v>
       </c>
       <c r="D2" t="n">
-        <v>23.8525422223805</v>
+        <v>24.4985322117749</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.1146278016854</v>
+        <v>28.26451640526567</v>
       </c>
       <c r="C3" t="n">
-        <v>82.22137023067037</v>
+        <v>50.60418541540184</v>
       </c>
       <c r="D3" t="n">
-        <v>88.88743714250622</v>
+        <v>84.16523068507905</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.51794618168159</v>
+        <v>27.22288209105981</v>
       </c>
       <c r="C4" t="n">
-        <v>110.282664861157</v>
+        <v>90.64083854229102</v>
       </c>
       <c r="D4" t="n">
-        <v>104.3224745486746</v>
+        <v>104.65430527271</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.85709110800325</v>
+        <v>37.13460691313561</v>
       </c>
       <c r="C5" t="n">
-        <v>103.1325963311275</v>
+        <v>74.83371875621313</v>
       </c>
       <c r="D5" t="n">
-        <v>57.35860962061991</v>
+        <v>64.35356201337844</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>24.95602664195392</v>
+        <v>34.77743067523902</v>
       </c>
       <c r="C6" t="n">
-        <v>145.9122525436822</v>
+        <v>89.11716610529999</v>
       </c>
       <c r="D6" t="n">
-        <v>28.86043726174349</v>
+        <v>31.95981476405067</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.70836417857646</v>
+        <v>24.852943133008</v>
       </c>
       <c r="C7" t="n">
-        <v>145.5843488104638</v>
+        <v>78.03225277664922</v>
       </c>
       <c r="D7" t="n">
-        <v>27.12863431145211</v>
+        <v>28.68568617038755</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.095892479846697</v>
+        <v>13.76901155206151</v>
       </c>
       <c r="C8" t="n">
-        <v>104.3106935762236</v>
+        <v>54.82570054366312</v>
       </c>
       <c r="D8" t="n">
-        <v>26.36974333606933</v>
+        <v>27.78836876870596</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>6.878124415953151</v>
       </c>
       <c r="C9" t="n">
-        <v>57.68749510154256</v>
+        <v>36.49843440078366</v>
       </c>
       <c r="D9" t="n">
-        <v>27.17968519207294</v>
+        <v>27.40156017323271</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.558835427894688</v>
+        <v>4.128249096357838</v>
       </c>
       <c r="C10" t="n">
-        <v>33.31069960509428</v>
+        <v>28.75539025738908</v>
       </c>
       <c r="D10" t="n">
-        <v>28.32833000604172</v>
+        <v>29.32480392585223</v>
       </c>
     </row>
     <row r="11">
@@ -1839,10 +1839,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.843141351498762</v>
+        <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>26.12136116689488</v>
+        <v>27.18753917370691</v>
       </c>
       <c r="D11" t="n">
         <v>28.25371718051895</v>
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.169662426385451</v>
+        <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>23.86628669023996</v>
+        <v>25.38505038870978</v>
       </c>
       <c r="D12" t="n">
-        <v>26.90381408717959</v>
+        <v>27.55471281509523</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>22.37403017978481</v>
+        <v>23.93500902953724</v>
       </c>
       <c r="D13" t="n">
-        <v>24.97566159603886</v>
+        <v>25.49598787928967</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.6145740628585034</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>19.97365704290136</v>
+        <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
-        <v>24.58296251434014</v>
+        <v>25.19753657719863</v>
       </c>
     </row>
     <row r="15">
@@ -1895,13 +1895,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.3583379120500857</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>18.27523351455437</v>
       </c>
       <c r="D15" t="n">
-        <v>22.21695054710532</v>
+        <v>23.29196428325557</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>16.94594712300419</v>
       </c>
       <c r="D16" t="n">
-        <v>20.25247339090745</v>
+        <v>20.66578917439536</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.58328130950962</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
-        <v>17.47216389248049</v>
+        <v>18.41660518396592</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>16.58662746324986</v>
       </c>
       <c r="D18" t="n">
-        <v>13.37631247036279</v>
+        <v>13.9113649691773</v>
       </c>
     </row>
     <row r="19">
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>72.62969516017901</v>
+        <v>75.31968386981528</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>7.397468951499714</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.413536767666159</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C2" t="n">
-        <v>4.435536127787089</v>
+        <v>2.589850443803086</v>
       </c>
       <c r="D2" t="n">
-        <v>17.10302675568368</v>
+        <v>17.32293824143497</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.6055016538088</v>
+        <v>29.95312245657018</v>
       </c>
       <c r="C3" t="n">
-        <v>62.07099860100459</v>
+        <v>34.43970946497811</v>
       </c>
       <c r="D3" t="n">
-        <v>87.79769719079225</v>
+        <v>84.52847733565038</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.6568145763369</v>
+        <v>39.06668639509333</v>
       </c>
       <c r="C4" t="n">
-        <v>157.9258992005504</v>
+        <v>111.878004880558</v>
       </c>
       <c r="D4" t="n">
-        <v>121.3989941163436</v>
+        <v>121.0161125116873</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.99868376159304</v>
+        <v>41.08614142272902</v>
       </c>
       <c r="C5" t="n">
-        <v>147.753029489145</v>
+        <v>118.8651032916826</v>
       </c>
       <c r="D5" t="n">
-        <v>73.21383504420589</v>
+        <v>80.69966128908783</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.02144388523996</v>
+        <v>41.53970886209105</v>
       </c>
       <c r="C6" t="n">
-        <v>160.8053652171063</v>
+        <v>105.5800933578148</v>
       </c>
       <c r="D6" t="n">
-        <v>34.97868895460962</v>
+        <v>39.56737772425921</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.57051858935441</v>
+        <v>23.65521093382689</v>
       </c>
       <c r="C7" t="n">
-        <v>175.8270868397867</v>
+        <v>100.3699582913769</v>
       </c>
       <c r="D7" t="n">
-        <v>29.58398531977338</v>
+        <v>31.38058361854505</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.677267047210056</v>
+        <v>11.43245201595411</v>
       </c>
       <c r="C8" t="n">
-        <v>133.2673421129833</v>
+        <v>72.34989706446869</v>
       </c>
       <c r="D8" t="n">
-        <v>27.12078032981814</v>
+        <v>28.95664853675967</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.104687151455913</v>
+        <v>5.324999547834698</v>
       </c>
       <c r="C9" t="n">
-        <v>59.79530742256046</v>
+        <v>42.3781214015178</v>
       </c>
       <c r="D9" t="n">
-        <v>28.06718511671205</v>
+        <v>28.51093507903161</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.992947839621025</v>
+        <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>34.44952694202058</v>
+        <v>32.02951885105219</v>
       </c>
       <c r="D10" t="n">
-        <v>29.46715734296802</v>
+        <v>30.32127784566274</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>28.60910984945629</v>
+        <v>30.38607319414302</v>
       </c>
       <c r="D11" t="n">
-        <v>29.31989518733098</v>
+        <v>29.49759152179966</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>22.1305567491316</v>
       </c>
       <c r="D12" t="n">
-        <v>27.77167905773377</v>
+        <v>28.63954402828795</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.2601631416254048</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.3902779224005</v>
+        <v>17.17076734727672</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>26.27647730416588</v>
       </c>
     </row>
     <row r="14">
@@ -2192,13 +2192,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>14.74977750860408</v>
+        <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>18.4372218857551</v>
+        <v>19.35908298004286</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>14.33351648200343</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.22610507161303</v>
+        <v>13.63942085510094</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>15.70599977254047</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>14.16661937228147</v>
       </c>
       <c r="D17" t="n">
-        <v>11.33329549782518</v>
+        <v>11.8055161435679</v>
       </c>
     </row>
     <row r="18">
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>63.19019098384595</v>
+        <v>65.59743635465912</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>6.018113427032947</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.774419012201486</v>
+        <v>5.631304831559704</v>
       </c>
       <c r="C2" t="n">
-        <v>5.677446973659304</v>
+        <v>4.070325981807276</v>
       </c>
       <c r="D2" t="n">
-        <v>18.59822850925158</v>
+        <v>15.63335044242621</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.64905840569416</v>
+        <v>23.70920705756047</v>
       </c>
       <c r="C3" t="n">
-        <v>39.67733346713484</v>
+        <v>21.35792130588936</v>
       </c>
       <c r="D3" t="n">
-        <v>81.74522259411067</v>
+        <v>79.0110552377833</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.00890214926301</v>
+        <v>48.49833658979244</v>
       </c>
       <c r="C4" t="n">
-        <v>156.2284574199077</v>
+        <v>98.40057239665781</v>
       </c>
       <c r="D4" t="n">
-        <v>134.1234261110865</v>
+        <v>134.3914432343459</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.4901795085222</v>
+        <v>49.50462798664542</v>
       </c>
       <c r="C5" t="n">
-        <v>213.5301256736813</v>
+        <v>162.601963515878</v>
       </c>
       <c r="D5" t="n">
-        <v>94.05143006684445</v>
+        <v>103.0344215607028</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.25415914887547</v>
+        <v>48.74475526355839</v>
       </c>
       <c r="C6" t="n">
-        <v>195.3010343012265</v>
+        <v>146.7172856611646</v>
       </c>
       <c r="D6" t="n">
-        <v>45.92713935237005</v>
+        <v>53.25294072145974</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.57725195456389</v>
+        <v>34.13536767666159</v>
       </c>
       <c r="C7" t="n">
-        <v>201.2190094624262</v>
+        <v>126.3008604036479</v>
       </c>
       <c r="D7" t="n">
-        <v>32.09922293805371</v>
+        <v>35.09355343600648</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.6814150222053</v>
+        <v>17.02350519163969</v>
       </c>
       <c r="C8" t="n">
-        <v>177.1612819698582</v>
+        <v>100.8058542720625</v>
       </c>
       <c r="D8" t="n">
-        <v>28.45595720759379</v>
+        <v>30.95941385342316</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>7.321874378272709</v>
       </c>
       <c r="C9" t="n">
-        <v>102.2843663146582</v>
+        <v>63.23436963053704</v>
       </c>
       <c r="D9" t="n">
-        <v>28.6218725696115</v>
+        <v>29.28749751309084</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.420008090968388</v>
+        <v>2.989421759431538</v>
       </c>
       <c r="C10" t="n">
-        <v>47.97310156802039</v>
+        <v>40.42837046088366</v>
       </c>
       <c r="D10" t="n">
-        <v>30.03657101143117</v>
+        <v>30.89069151412589</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>33.22921454564179</v>
+        <v>33.93999988351647</v>
       </c>
       <c r="D11" t="n">
-        <v>29.852984190737</v>
+        <v>30.20837685967435</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>24.0832529328785</v>
+        <v>26.68684784454105</v>
       </c>
       <c r="D12" t="n">
-        <v>28.20561154301086</v>
+        <v>29.07347651356504</v>
       </c>
     </row>
     <row r="13">
@@ -2489,13 +2489,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.47158305540374</v>
+        <v>19.77239876353076</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>26.53664044579129</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>15.67163860289184</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>20.28094407433061</v>
       </c>
     </row>
     <row r="15">
@@ -2523,7 +2523,7 @@
         <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
-        <v>16.84188186635403</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.05273663858884</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="D16" t="n">
-        <v>14.46605242207675</v>
+        <v>15.29268398905256</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>15.11106066376691</v>
       </c>
       <c r="D17" t="n">
-        <v>10.38885420633975</v>
+        <v>11.33329549782518</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>33.09962384868121</v>
+        <v>35.50686921949439</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>4.212679398923063</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.701368771459722</v>
+        <v>3.322234231171206</v>
       </c>
       <c r="C2" t="n">
-        <v>2.810743677258618</v>
+        <v>1.899681807717578</v>
       </c>
       <c r="D2" t="n">
-        <v>13.12007631955437</v>
+        <v>10.79038901737669</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.75075925630833</v>
+        <v>23.92519155249477</v>
       </c>
       <c r="C3" t="n">
-        <v>35.13675033499334</v>
+        <v>20.12091919853838</v>
       </c>
       <c r="D3" t="n">
-        <v>81.12181280191395</v>
+        <v>77.01810739816227</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.9953786655818</v>
+        <v>53.70552641311752</v>
       </c>
       <c r="C4" t="n">
-        <v>152.1826751307066</v>
+        <v>91.91711055781187</v>
       </c>
       <c r="D4" t="n">
-        <v>143.4402118243887</v>
+        <v>143.5678390259408</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.61918936840603</v>
+        <v>52.15534678811181</v>
       </c>
       <c r="C5" t="n">
-        <v>266.1763463139165</v>
+        <v>190.4590546238812</v>
       </c>
       <c r="D5" t="n">
-        <v>96.72669256091702</v>
+        <v>112.0174130545611</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>26.96860943565989</v>
+        <v>41.45920555034281</v>
       </c>
       <c r="C6" t="n">
-        <v>227.2608490652772</v>
+        <v>181.7362262716483</v>
       </c>
       <c r="D6" t="n">
-        <v>45.08185457901354</v>
+        <v>52.48815925985148</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.066619975168541</v>
+        <v>11.25868267230242</v>
       </c>
       <c r="C7" t="n">
-        <v>217.8674870310437</v>
+        <v>133.6070268186527</v>
       </c>
       <c r="D7" t="n">
-        <v>32.27888276793088</v>
+        <v>35.45287309576081</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.588287859022091</v>
+        <v>5.006913291658733</v>
       </c>
       <c r="C8" t="n">
-        <v>124.0045525234146</v>
+        <v>78.1912959047372</v>
       </c>
       <c r="D8" t="n">
-        <v>30.29182541453534</v>
+        <v>32.12769362147687</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.664062358698343</v>
+        <v>2.107812321017901</v>
       </c>
       <c r="C9" t="n">
-        <v>36.60937189136354</v>
+        <v>30.84062238120929</v>
       </c>
       <c r="D9" t="n">
-        <v>31.06249736236907</v>
+        <v>32.39374724932775</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>26.05067533218912</v>
+        <v>26.62008900065227</v>
       </c>
       <c r="D10" t="n">
-        <v>23.34596040698915</v>
+        <v>23.63066724122073</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>19.19120412261664</v>
+        <v>21.32356013624072</v>
       </c>
       <c r="D11" t="n">
-        <v>22.56743447752142</v>
+        <v>23.27821981539612</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>14.97067074205961</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>21.47965802121596</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>12.74799393964483</v>
+        <v>13.52848336452105</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>16.65044106402591</v>
       </c>
     </row>
     <row r="14">
@@ -2820,7 +2820,7 @@
         <v>13.21334235145782</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>14.74977750860408</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>11.82515109765283</v>
+        <v>12.541826921753</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>12.90016483380309</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>12.81278928812512</v>
       </c>
       <c r="D16" t="n">
-        <v>8.679631453246051</v>
+        <v>9.506263020221864</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>30.22212132753381</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>28.35778243716912</v>
+        <v>30.49799243242716</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>3.21031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.630102099677205</v>
+        <v>4.270602513473626</v>
       </c>
       <c r="C2" t="n">
-        <v>9.673160129943822</v>
+        <v>2.710605411425443</v>
       </c>
       <c r="D2" t="n">
-        <v>15.24359660384022</v>
+        <v>10.90623524647782</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.49979169691964</v>
+        <v>17.80890335503714</v>
       </c>
       <c r="C3" t="n">
-        <v>23.49813130114741</v>
+        <v>13.33704256219292</v>
       </c>
       <c r="D3" t="n">
-        <v>74.58828183015142</v>
+        <v>68.70270434319178</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.05995302988384</v>
+        <v>50.01710028826225</v>
       </c>
       <c r="C4" t="n">
-        <v>122.1519946055009</v>
+        <v>71.49675830947821</v>
       </c>
       <c r="D4" t="n">
-        <v>148.7877915694211</v>
+        <v>148.4431981252305</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.92691836819179</v>
+        <v>64.84443586550184</v>
       </c>
       <c r="C5" t="n">
-        <v>274.3739396443774</v>
+        <v>181.9914806747525</v>
       </c>
       <c r="D5" t="n">
-        <v>117.8588118948296</v>
+        <v>133.8122120888403</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.77743067523902</v>
+        <v>53.65545728020094</v>
       </c>
       <c r="C6" t="n">
-        <v>309.897498574844</v>
+        <v>238.2092994630376</v>
       </c>
       <c r="D6" t="n">
-        <v>58.64666260859173</v>
+        <v>71.20517924131691</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>14.55244622005047</v>
+        <v>24.01453059358123</v>
       </c>
       <c r="C7" t="n">
-        <v>266.794847367592</v>
+        <v>192.4156777984451</v>
       </c>
       <c r="D7" t="n">
-        <v>36.35117224514665</v>
+        <v>40.48334833232147</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.589670517353839</v>
+        <v>7.009678608322226</v>
       </c>
       <c r="C8" t="n">
-        <v>186.1737258948439</v>
+        <v>119.8321247803657</v>
       </c>
       <c r="D8" t="n">
-        <v>31.71045084717197</v>
+        <v>34.13045893814036</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>2.773437264497239</v>
       </c>
       <c r="C9" t="n">
-        <v>75.32655610374501</v>
+        <v>56.02343274284421</v>
       </c>
       <c r="D9" t="n">
-        <v>31.72812230584841</v>
+        <v>33.28124717396686</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>1.423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>31.8871654339364</v>
+        <v>31.31775176547326</v>
       </c>
       <c r="D10" t="n">
-        <v>24.20008090968388</v>
+        <v>25.19655482949439</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>22.56743447752142</v>
+        <v>24.87748682561417</v>
       </c>
       <c r="D11" t="n">
-        <v>23.45591614986479</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.14033316844506</v>
+        <v>18.44213062427633</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>21.91359050649305</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>14.30897278939726</v>
+        <v>15.86995163914969</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>16.65044106402591</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.82791641431633</v>
+        <v>14.13520344574558</v>
       </c>
       <c r="D14" t="n">
-        <v>13.82791641431633</v>
+        <v>14.74977750860408</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.90016483380309</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="D15" t="n">
-        <v>11.46681318560274</v>
+        <v>12.18348900970292</v>
       </c>
     </row>
     <row r="16">
@@ -3156,10 +3156,10 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.97231544229862</v>
+        <v>24.38563122578652</v>
       </c>
       <c r="D16" t="n">
-        <v>7.852999886270235</v>
+        <v>8.266315669758143</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.0554452019901</v>
+        <v>34.94432778496098</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.841758693167016</v>
+        <v>3.201479263548849</v>
       </c>
       <c r="C2" t="n">
-        <v>5.017712516405448</v>
+        <v>2.171625921793944</v>
       </c>
       <c r="D2" t="n">
-        <v>11.78980818029994</v>
+        <v>8.249625958785947</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.896016858807849</v>
+        <v>16.61607989437726</v>
       </c>
       <c r="C3" t="n">
-        <v>29.6242369756475</v>
+        <v>12.15403657857551</v>
       </c>
       <c r="D3" t="n">
-        <v>71.5448639469863</v>
+        <v>63.26382206166446</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.12903522207961</v>
+        <v>44.60570694245383</v>
       </c>
       <c r="C4" t="n">
-        <v>100.2639295393183</v>
+        <v>56.5133248472634</v>
       </c>
       <c r="D4" t="n">
-        <v>150.8808776748753</v>
+        <v>149.4004021368711</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.19122948481243</v>
+        <v>71.17670855789376</v>
       </c>
       <c r="C5" t="n">
-        <v>263.6728896680871</v>
+        <v>168.516993433965</v>
       </c>
       <c r="D5" t="n">
-        <v>131.5541923690726</v>
+        <v>149.765612282851</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.60762938013333</v>
+        <v>63.87937787222722</v>
       </c>
       <c r="C6" t="n">
-        <v>362.1441478994507</v>
+        <v>267.2709950041517</v>
       </c>
       <c r="D6" t="n">
-        <v>69.99762956509335</v>
+        <v>84.52847733565039</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>12.81573453123786</v>
+        <v>22.57725195456389</v>
       </c>
       <c r="C7" t="n">
-        <v>326.8611171565245</v>
+        <v>246.7927196412674</v>
       </c>
       <c r="D7" t="n">
-        <v>39.88448223273092</v>
+        <v>45.57371017884118</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.67173641388307</v>
+        <v>5.674501730546564</v>
       </c>
       <c r="C8" t="n">
-        <v>229.9842171968578</v>
+        <v>156.6329374740573</v>
       </c>
       <c r="D8" t="n">
-        <v>32.12769362147687</v>
+        <v>36.04977569994287</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.553124868118454</v>
+        <v>2.107812321017901</v>
       </c>
       <c r="C9" t="n">
-        <v>79.5421807457808</v>
+        <v>67.00624431025328</v>
       </c>
       <c r="D9" t="n">
-        <v>31.39530983410874</v>
+        <v>33.05937219280708</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.2847068342315751</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>31.74481201682062</v>
+        <v>32.59893251951534</v>
       </c>
       <c r="D10" t="n">
-        <v>24.62714116103124</v>
+        <v>25.62361508084176</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.0343454741154</v>
+        <v>24.6997904911455</v>
       </c>
       <c r="D11" t="n">
-        <v>23.63361248433346</v>
+        <v>24.34439782220815</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.62156946997525</v>
+        <v>17.7912318963607</v>
       </c>
       <c r="D12" t="n">
-        <v>19.7439280801076</v>
+        <v>20.61179305066178</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.44717823151781</v>
+        <v>11.70734137314322</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>16.65044106402591</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>10.75504610002381</v>
+        <v>11.36962016288231</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>11.67690719431156</v>
       </c>
     </row>
     <row r="15">
@@ -3453,10 +3453,10 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>20.42526098685489</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>6.808420328951629</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.10547327717769</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
         <v>0.4722206457427158</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.39153740754523</v>
+        <v>5.901285450227578</v>
       </c>
       <c r="C2" t="n">
-        <v>5.805074175211389</v>
+        <v>5.613633372883262</v>
       </c>
       <c r="D2" t="n">
-        <v>13.8357703959503</v>
+        <v>16.5748464907989</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>8.153414683769761</v>
+        <v>13.78373776762522</v>
       </c>
       <c r="C3" t="n">
-        <v>25.00511402716626</v>
+        <v>10.29362467902781</v>
       </c>
       <c r="D3" t="n">
-        <v>65.66910393706915</v>
+        <v>56.90209693814514</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.76418492899829</v>
+        <v>38.31368590593603</v>
       </c>
       <c r="C4" t="n">
-        <v>89.01997308257953</v>
+        <v>44.32492709903924</v>
       </c>
       <c r="D4" t="n">
-        <v>151.0085048764274</v>
+        <v>145.5843488104638</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.01313223971626</v>
+        <v>70.29313562407164</v>
       </c>
       <c r="C5" t="n">
-        <v>231.643370817035</v>
+        <v>139.7272420069273</v>
       </c>
       <c r="D5" t="n">
-        <v>147.3357867148401</v>
+        <v>165.0072453912827</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>46.65166915810419</v>
+        <v>76.3976428490783</v>
       </c>
       <c r="C6" t="n">
-        <v>384.2825586302163</v>
+        <v>271.1754056239413</v>
       </c>
       <c r="D6" t="n">
-        <v>85.89703363537045</v>
+        <v>105.0568218314512</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>23.2360046641135</v>
+        <v>40.90255460203486</v>
       </c>
       <c r="C7" t="n">
-        <v>399.3838018169407</v>
+        <v>304.3437518119197</v>
       </c>
       <c r="D7" t="n">
-        <v>46.35223610830891</v>
+        <v>55.27534099220816</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.508987279156353</v>
+        <v>11.51590057081509</v>
       </c>
       <c r="C8" t="n">
-        <v>305.0044680168778</v>
+        <v>225.9786865635308</v>
       </c>
       <c r="D8" t="n">
-        <v>34.04701038327938</v>
+        <v>38.88702656521616</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>3.106249736236907</v>
       </c>
       <c r="C9" t="n">
-        <v>146.7703000371938</v>
+        <v>113.9328028255466</v>
       </c>
       <c r="D9" t="n">
-        <v>32.06093477758807</v>
+        <v>34.27968458918587</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0.8541205026947251</v>
       </c>
       <c r="C10" t="n">
-        <v>50.53546307610457</v>
+        <v>49.82369599052563</v>
       </c>
       <c r="D10" t="n">
-        <v>25.48126166372597</v>
+        <v>27.18950266911542</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>26.29905750136355</v>
+        <v>29.31989518733098</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>24.52209415667683</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.22516438163779</v>
+        <v>21.04572553593887</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>21.04572553593887</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>12.74799393964483</v>
+        <v>13.78864650614645</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>16.91060420565131</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>11.98419422574081</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>11.98419422574081</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>21.50027472300514</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>6.091744504851459</v>
+        <v>6.450082416901544</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>26.03889435973815</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.5553093477052</v>
+        <v>7.716536955379929</v>
       </c>
       <c r="C2" t="n">
-        <v>16.22534430808703</v>
+        <v>4.730060439061132</v>
       </c>
       <c r="D2" t="n">
-        <v>5.89735845941059</v>
+        <v>7.745989386507333</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.764200624531518</v>
+        <v>4.174391238457438</v>
       </c>
       <c r="C2" t="n">
-        <v>3.483240854667684</v>
+        <v>3.143556148998286</v>
       </c>
       <c r="D2" t="n">
-        <v>10.4045621696077</v>
+        <v>12.19821522526662</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.90230825566083</v>
+        <v>19.09499284760046</v>
       </c>
       <c r="C3" t="n">
-        <v>28.78484268851648</v>
+        <v>15.42816517223863</v>
       </c>
       <c r="D3" t="n">
-        <v>70.82327938436491</v>
+        <v>63.69088231301183</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.56595400819845</v>
+        <v>53.30988208830605</v>
       </c>
       <c r="C4" t="n">
-        <v>129.74581309785</v>
+        <v>67.24677249779377</v>
       </c>
       <c r="D4" t="n">
-        <v>152.4889804144316</v>
+        <v>149.7449955810617</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26.26175108860219</v>
+        <v>45.62672455487052</v>
       </c>
       <c r="C5" t="n">
-        <v>332.9106465100934</v>
+        <v>220.549621759046</v>
       </c>
       <c r="D5" t="n">
-        <v>130.8424252834937</v>
+        <v>151.7781950765569</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>14.41009280293469</v>
+        <v>25.39879485656924</v>
       </c>
       <c r="C6" t="n">
-        <v>327.0849556330929</v>
+        <v>256.2420412946431</v>
       </c>
       <c r="D6" t="n">
-        <v>68.10580173900973</v>
+        <v>82.75740447718914</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4.311835917051991</v>
+        <v>7.60559946480004</v>
       </c>
       <c r="C7" t="n">
-        <v>214.4539502633775</v>
+        <v>158.8791762213741</v>
       </c>
       <c r="D7" t="n">
-        <v>29.34443887993716</v>
+        <v>34.91389360612931</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.335176877775662</v>
+        <v>2.086213871524472</v>
       </c>
       <c r="C8" t="n">
-        <v>108.1493270998286</v>
+        <v>83.94924619014475</v>
       </c>
       <c r="D8" t="n">
-        <v>23.61594102565702</v>
+        <v>25.20146356801562</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.2218749811597791</v>
+        <v>0.5546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>38.49530923122167</v>
+        <v>38.05155926890212</v>
       </c>
       <c r="D9" t="n">
-        <v>19.41406085148067</v>
+        <v>20.74531073843935</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>20.64124548178919</v>
+        <v>22.91890015564179</v>
       </c>
       <c r="D10" t="n">
-        <v>18.79065105928395</v>
+        <v>19.21771131063132</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>14.57109942643116</v>
+        <v>16.8811517745239</v>
       </c>
       <c r="D11" t="n">
-        <v>15.99267010218054</v>
+        <v>16.8811517745239</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.41437964665016</v>
+        <v>11.0652783745658</v>
       </c>
       <c r="D12" t="n">
-        <v>12.80100831567416</v>
+        <v>13.66887328622834</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.365873098514571</v>
+        <v>9.886199381765381</v>
       </c>
       <c r="D13" t="n">
-        <v>8.845546815263763</v>
+        <v>9.886199381765381</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>17.8226478228966</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>4.916592502868027</v>
+        <v>5.223879534297279</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>21.85861263505523</v>
+        <v>24.72531593145592</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.574764375340889</v>
+        <v>7.214863878509809</v>
       </c>
       <c r="C2" t="n">
-        <v>8.51666133434108</v>
+        <v>4.288273972150068</v>
       </c>
       <c r="D2" t="n">
-        <v>6.300856765856029</v>
+        <v>20.83759502263855</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.680032363873551</v>
+        <v>16.38536918387927</v>
       </c>
       <c r="C3" t="n">
-        <v>40.88488314335842</v>
+        <v>11.91841712955628</v>
       </c>
       <c r="D3" t="n">
-        <v>8.089601082993717</v>
+        <v>9.64076245570368</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.454950097693773</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>4.68784528777852</v>
       </c>
       <c r="C5" t="n">
-        <v>9.35114688295087</v>
+        <v>9.424777960769381</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>8.130834486572086</v>
       </c>
       <c r="C6" t="n">
         <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>32.52333794628834</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>32.69808903764427</v>
       </c>
     </row>
     <row r="8">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39742247980036</v>
+        <v>13.3985356936788</v>
       </c>
       <c r="C21" t="n">
-        <v>70.13944710013129</v>
+        <v>70.14527510220074</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576167350564748</v>
+        <v>1.576298316903388</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.703553251046468</v>
+        <v>5.363287708300325</v>
       </c>
       <c r="C2" t="n">
-        <v>8.203483816686347</v>
+        <v>5.105088062083413</v>
       </c>
       <c r="D2" t="n">
-        <v>19.63495408493621</v>
+        <v>15.96910815727862</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.45056544298705</v>
+        <v>21.55427084673872</v>
       </c>
       <c r="C3" t="n">
-        <v>36.08413686959152</v>
+        <v>14.92256510455152</v>
       </c>
       <c r="D3" t="n">
-        <v>11.42754327743287</v>
+        <v>24.81367322483813</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>11.37158365829081</v>
+        <v>18.93987671032947</v>
       </c>
       <c r="C4" t="n">
-        <v>62.83087132409162</v>
+        <v>18.71014774753571</v>
       </c>
       <c r="D4" t="n">
-        <v>19.30999559483051</v>
+        <v>20.12680968476386</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>3.043417883165113</v>
       </c>
       <c r="C5" t="n">
-        <v>5.473243451175969</v>
+        <v>5.375068680751288</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>29.10881943091793</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.34217228489241</v>
+        <v>16.54343056426301</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>34.77743067523902</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.521970983489814</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>35.27321326588365</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>36.80081269369168</v>
       </c>
     </row>
     <row r="9">
@@ -4921,7 +4921,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>9.318749208710722</v>
       </c>
       <c r="C9" t="n">
         <v>25.73749781453438</v>
@@ -4935,10 +4935,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>8.968265278294615</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>27.04714925199963</v>
       </c>
       <c r="D10" t="n">
         <v>50.1084028247572</v>
@@ -4952,7 +4952,7 @@
         <v>7.640942382152923</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
         <v>47.97801030654161</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>5.0167307687012</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5022,10 +5022,10 @@
         <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>40.5049467818149</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>5.66664774891259</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43835584477201</v>
+        <v>15.44144146787245</v>
       </c>
       <c r="C21" t="n">
-        <v>86.1297747129386</v>
+        <v>86.14698924181475</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250180177846739</v>
+        <v>3.250829782709991</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.494440990041897</v>
+        <v>5.048146695237099</v>
       </c>
       <c r="C2" t="n">
-        <v>6.039711876526377</v>
+        <v>5.499750639190632</v>
       </c>
       <c r="D2" t="n">
-        <v>27.68430351205581</v>
+        <v>18.66007861461912</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.75843331149305</v>
+        <v>19.87548227247668</v>
       </c>
       <c r="C3" t="n">
-        <v>33.58068022376215</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="D3" t="n">
-        <v>24.47987900539422</v>
+        <v>31.82826057168159</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.68760860806704</v>
+        <v>31.77917318646925</v>
       </c>
       <c r="C4" t="n">
-        <v>78.77150879794708</v>
+        <v>29.69884980117026</v>
       </c>
       <c r="D4" t="n">
-        <v>20.71389481190345</v>
+        <v>28.02693346083794</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>10.30835089459151</v>
+        <v>16.39518666092174</v>
       </c>
       <c r="C5" t="n">
-        <v>67.29880512611886</v>
+        <v>21.94206118991621</v>
       </c>
       <c r="D5" t="n">
-        <v>29.91876128692155</v>
+        <v>29.67332436085985</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.916993413495527</v>
+        <v>5.876741757621407</v>
       </c>
       <c r="C6" t="n">
-        <v>12.23650338573225</v>
+        <v>12.19625172985813</v>
       </c>
       <c r="D6" t="n">
-        <v>36.10573531908495</v>
+        <v>36.6290068454485</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.37385025333556</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>37.42913122440964</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>10.34762080276138</v>
       </c>
       <c r="C8" t="n">
-        <v>29.79113408536946</v>
+        <v>29.87458264023044</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>38.55323234577224</v>
       </c>
     </row>
     <row r="9">
@@ -5235,10 +5235,10 @@
         <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
-        <v>29.39843500367073</v>
+        <v>29.50937249425062</v>
       </c>
       <c r="D9" t="n">
-        <v>41.15780900513902</v>
+        <v>41.26874649571891</v>
       </c>
     </row>
     <row r="10">
@@ -5246,7 +5246,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>9.537678946757763</v>
       </c>
       <c r="C10" t="n">
         <v>29.89421759431538</v>
@@ -5277,10 +5277,10 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>31.67707142522758</v>
+        <v>32.11100391050467</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>45.77987719673301</v>
       </c>
     </row>
     <row r="13">
@@ -5294,7 +5294,7 @@
         <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>45.52854978444583</v>
       </c>
     </row>
     <row r="14">
@@ -5305,7 +5305,7 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>27.65583282863265</v>
       </c>
       <c r="D14" t="n">
         <v>45.47848065152925</v>
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
         <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>43.00054944601029</v>
       </c>
     </row>
     <row r="16">
@@ -5350,7 +5350,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72483000168812</v>
+        <v>16.73686262671233</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0214630102975</v>
+        <v>102.0948620229452</v>
       </c>
       <c r="D21" t="n">
-        <v>4.181207500422031</v>
+        <v>5.021058788013698</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.340306600475149</v>
+        <v>5.756968537703296</v>
       </c>
       <c r="C2" t="n">
-        <v>7.352308557104362</v>
+        <v>5.793293202760428</v>
       </c>
       <c r="D2" t="n">
-        <v>34.29539255245383</v>
+        <v>23.94384475887546</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.97794388661684</v>
+        <v>18.46176557836127</v>
       </c>
       <c r="C3" t="n">
-        <v>27.7932775072272</v>
+        <v>19.88529974951915</v>
       </c>
       <c r="D3" t="n">
-        <v>40.0749412873548</v>
+        <v>38.93120521190727</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.37152690502857</v>
+        <v>35.30168394930681</v>
       </c>
       <c r="C4" t="n">
-        <v>81.63035811271379</v>
+        <v>37.86699070050372</v>
       </c>
       <c r="D4" t="n">
-        <v>27.91206897944107</v>
+        <v>36.88426124855267</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>22.48202242725196</v>
+        <v>32.42221793275092</v>
       </c>
       <c r="C5" t="n">
-        <v>108.7285582453343</v>
+        <v>40.05530633326987</v>
       </c>
       <c r="D5" t="n">
-        <v>30.704159450319</v>
+        <v>33.1830724035422</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>9.94215900090745</v>
+        <v>14.00757624419349</v>
       </c>
       <c r="C6" t="n">
-        <v>60.01521890831177</v>
+        <v>24.15099352447154</v>
       </c>
       <c r="D6" t="n">
-        <v>37.35353665118265</v>
+        <v>38.19882142453915</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.563785224144926</v>
+        <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>21.31963314542373</v>
+        <v>21.02020009562846</v>
       </c>
       <c r="D7" t="n">
-        <v>39.76470901281281</v>
+        <v>39.46527596301753</v>
       </c>
     </row>
     <row r="8">
@@ -5532,10 +5532,10 @@
         <v>10.76486357706628</v>
       </c>
       <c r="C8" t="n">
-        <v>31.37665662772806</v>
+        <v>31.87734795689393</v>
       </c>
       <c r="D8" t="n">
-        <v>39.30426933952106</v>
+        <v>40.38910055271378</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>34.05780960802609</v>
+        <v>34.27968458918587</v>
       </c>
       <c r="D9" t="n">
-        <v>42.15624642035802</v>
+        <v>41.93437143919824</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.31069960509428</v>
+        <v>33.16834618797849</v>
       </c>
       <c r="D10" t="n">
-        <v>48.68486865359933</v>
+        <v>49.25428232206248</v>
       </c>
     </row>
     <row r="11">
@@ -5571,10 +5571,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>9.062513057902304</v>
       </c>
       <c r="C11" t="n">
-        <v>33.40691088011046</v>
+        <v>33.7623035490478</v>
       </c>
       <c r="D11" t="n">
         <v>50.82115165804038</v>
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.159886007071988</v>
+        <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.49763257952867</v>
       </c>
       <c r="D12" t="n">
-        <v>47.73257338047992</v>
+        <v>46.86470840992573</v>
       </c>
     </row>
     <row r="13">
@@ -5605,7 +5605,7 @@
         <v>33.04071898642641</v>
       </c>
       <c r="D13" t="n">
-        <v>45.26838664282043</v>
+        <v>46.30903920932205</v>
       </c>
     </row>
     <row r="14">
@@ -5616,10 +5616,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5630,7 +5630,7 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.38370878810703</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
         <v>43.71722527011046</v>
@@ -5644,10 +5644,10 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.77765165941727</v>
       </c>
     </row>
     <row r="18">
@@ -5689,7 +5689,7 @@
         <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
-        <v>25.27607639353838</v>
+        <v>24.67426505083508</v>
       </c>
     </row>
     <row r="20">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.03685049348418</v>
+        <v>18.06672272143762</v>
       </c>
       <c r="C21" t="n">
-        <v>117.6689770289206</v>
+        <v>117.8638577541407</v>
       </c>
       <c r="D21" t="n">
-        <v>6.01228349782806</v>
+        <v>6.88256103673814</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.141232800691299</v>
+        <v>7.885397560510381</v>
       </c>
       <c r="C2" t="n">
-        <v>5.977861771158828</v>
+        <v>5.486006171331176</v>
       </c>
       <c r="D2" t="n">
-        <v>27.81094896590364</v>
+        <v>23.01412968295373</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.59720570381833</v>
+        <v>17.16094987023424</v>
       </c>
       <c r="C3" t="n">
-        <v>26.41392198276044</v>
+        <v>20.15037162966578</v>
       </c>
       <c r="D3" t="n">
-        <v>52.82784396552087</v>
+        <v>45.59727212374311</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.58175978245763</v>
+        <v>26.03594911662541</v>
       </c>
       <c r="C4" t="n">
-        <v>62.00129451400306</v>
+        <v>37.42029549507142</v>
       </c>
       <c r="D4" t="n">
-        <v>34.85498874387451</v>
+        <v>41.1214843400819</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>19.61041039233004</v>
+        <v>26.23720739599601</v>
       </c>
       <c r="C5" t="n">
-        <v>97.11939164261574</v>
+        <v>41.94517066394498</v>
       </c>
       <c r="D5" t="n">
-        <v>27.3171298706675</v>
+        <v>31.66136346195964</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.82769543013807</v>
+        <v>16.02015903789946</v>
       </c>
       <c r="C6" t="n">
-        <v>78.93349716914781</v>
+        <v>30.18874190558942</v>
       </c>
       <c r="D6" t="n">
-        <v>29.7057220351</v>
+        <v>30.87302005544945</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.150248456478767</v>
+        <v>6.347980655659875</v>
       </c>
       <c r="C7" t="n">
-        <v>33.77604801690726</v>
+        <v>18.20552942755285</v>
       </c>
       <c r="D7" t="n">
-        <v>31.02126395879071</v>
+        <v>31.14103717870882</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.756567627075796</v>
+        <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.60902773399829</v>
+        <v>18.52557917913731</v>
       </c>
       <c r="D8" t="n">
-        <v>29.37389131106456</v>
+        <v>30.37527396939631</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.77031209493525</v>
+        <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>21.63281066307846</v>
+        <v>22.2984356065578</v>
       </c>
       <c r="D9" t="n">
-        <v>30.17499743772996</v>
+        <v>29.95312245657017</v>
       </c>
     </row>
     <row r="10">
@@ -5871,10 +5871,10 @@
         <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>21.49536598448391</v>
       </c>
       <c r="D10" t="n">
-        <v>33.16834618797849</v>
+        <v>33.73775985644164</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.07968579496001</v>
+        <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
-        <v>34.65078522139116</v>
+        <v>34.47308888692249</v>
       </c>
     </row>
     <row r="12">
@@ -5899,7 +5899,7 @@
         <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>20.17786056538469</v>
       </c>
       <c r="D12" t="n">
         <v>32.11100391050467</v>
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.081305133003238</v>
+        <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
         <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
-        <v>30.17892442854696</v>
+        <v>30.43908757017236</v>
       </c>
     </row>
     <row r="14">
@@ -5944,7 +5944,7 @@
         <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
-        <v>27.95035713990669</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -5958,7 +5958,7 @@
         <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -5969,10 +5969,10 @@
         <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
-        <v>23.13881164139307</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.04220247504499</v>
+        <v>7.063365983468009</v>
       </c>
       <c r="C21" t="n">
-        <v>66.02064820354678</v>
+        <v>66.21905609501259</v>
       </c>
       <c r="D21" t="n">
-        <v>4.401376546903119</v>
+        <v>5.297524487601007</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.821362975556085</v>
+        <v>5.722607368054658</v>
       </c>
       <c r="C2" t="n">
-        <v>5.734388340505619</v>
+        <v>5.486987919035423</v>
       </c>
       <c r="D2" t="n">
-        <v>26.46399111567702</v>
+        <v>29.0872209814245</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.24363766156923</v>
+        <v>23.75338570425158</v>
       </c>
       <c r="C3" t="n">
-        <v>24.71058971589222</v>
+        <v>21.00449213236051</v>
       </c>
       <c r="D3" t="n">
-        <v>63.42581043286518</v>
+        <v>54.39373155379454</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.54271085846601</v>
+        <v>31.16656261901924</v>
       </c>
       <c r="C4" t="n">
-        <v>64.01780429852602</v>
+        <v>45.83092807735385</v>
       </c>
       <c r="D4" t="n">
-        <v>54.45852690227482</v>
+        <v>56.2197822836936</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.09623663721197</v>
+        <v>34.28753857081986</v>
       </c>
       <c r="C5" t="n">
-        <v>107.820441618906</v>
+        <v>58.51216317310991</v>
       </c>
       <c r="D5" t="n">
-        <v>33.84575210390879</v>
+        <v>40.25165587411923</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>19.64280806657019</v>
+        <v>27.4113776502752</v>
       </c>
       <c r="C6" t="n">
-        <v>122.6870471043154</v>
+        <v>52.40765594810324</v>
       </c>
       <c r="D6" t="n">
-        <v>32.16107304342126</v>
+        <v>34.17365583712723</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>13.89369351050086</v>
       </c>
       <c r="C7" t="n">
-        <v>79.64919124554372</v>
+        <v>33.59638818703009</v>
       </c>
       <c r="D7" t="n">
-        <v>33.11729530735765</v>
+        <v>33.71616140694821</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.424156065963627</v>
+        <v>6.258641614573416</v>
       </c>
       <c r="C8" t="n">
-        <v>33.62976760897448</v>
+        <v>22.28076414788136</v>
       </c>
       <c r="D8" t="n">
-        <v>31.2097595180061</v>
+        <v>32.46148784092078</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.992187076095029</v>
+        <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
-        <v>23.18593553119691</v>
+        <v>23.51874800293658</v>
       </c>
       <c r="D9" t="n">
-        <v>31.39530983410874</v>
+        <v>31.17343485294896</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>24.20008090968388</v>
+        <v>25.0542014123786</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>34.16482010778901</v>
       </c>
     </row>
     <row r="11">
@@ -6196,7 +6196,7 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.10052348092744</v>
+        <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
         <v>35.00617789032851</v>
@@ -6210,10 +6210,10 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>21.91359050649305</v>
+        <v>22.34752299177014</v>
       </c>
       <c r="D12" t="n">
-        <v>33.1958351236974</v>
+        <v>33.41280136633594</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>21.07321447165778</v>
+        <v>21.33337761328319</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>31.21957699504857</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>19.35908298004286</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -6252,10 +6252,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -6280,10 +6280,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -6311,7 +6311,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.256862183898595</v>
+        <v>7.289726459358568</v>
       </c>
       <c r="C21" t="n">
-        <v>75.28994515794793</v>
+        <v>76.54212782326498</v>
       </c>
       <c r="D21" t="n">
-        <v>5.442646637923946</v>
+        <v>6.378510651938748</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.243113577754714</v>
+        <v>5.075635630956009</v>
       </c>
       <c r="C2" t="n">
-        <v>12.42205370183489</v>
+        <v>6.862416452685205</v>
       </c>
       <c r="D2" t="n">
-        <v>30.25059201095697</v>
+        <v>25.22208026980481</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.20160243673586</v>
+        <v>21.56408832378119</v>
       </c>
       <c r="C3" t="n">
-        <v>23.27232932917064</v>
+        <v>21.23029410433728</v>
       </c>
       <c r="D3" t="n">
-        <v>69.42919764433444</v>
+        <v>65.04078540635119</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.36625831360885</v>
+        <v>40.11322944782042</v>
       </c>
       <c r="C4" t="n">
-        <v>62.8053458837812</v>
+        <v>49.92776124717579</v>
       </c>
       <c r="D4" t="n">
-        <v>72.41567416065323</v>
+        <v>70.32258805519903</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.49584901056943</v>
+        <v>41.28249096357838</v>
       </c>
       <c r="C5" t="n">
-        <v>113.6372967665683</v>
+        <v>73.77833997414781</v>
       </c>
       <c r="D5" t="n">
-        <v>45.7248993252952</v>
+        <v>52.05717201768713</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.37741739125406</v>
+        <v>38.31957639216151</v>
       </c>
       <c r="C6" t="n">
-        <v>147.6430737462694</v>
+        <v>74.66682164649117</v>
       </c>
       <c r="D6" t="n">
-        <v>35.74347041621788</v>
+        <v>39.48687441251096</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.76825078853552</v>
+        <v>24.13430381349934</v>
       </c>
       <c r="C7" t="n">
-        <v>131.9900883497582</v>
+        <v>57.49114556069321</v>
       </c>
       <c r="D7" t="n">
-        <v>34.85400699617026</v>
+        <v>36.05173919535137</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.927612711792993</v>
+        <v>11.18210635137117</v>
       </c>
       <c r="C8" t="n">
-        <v>71.5154115158589</v>
+        <v>34.96494448675015</v>
       </c>
       <c r="D8" t="n">
-        <v>33.37942194439155</v>
+        <v>34.63115026730623</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.435937038414587</v>
+        <v>5.990624491314035</v>
       </c>
       <c r="C9" t="n">
-        <v>33.05937219280708</v>
+        <v>26.5140602485936</v>
       </c>
       <c r="D9" t="n">
-        <v>32.28280975874785</v>
+        <v>32.50468473990763</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
-        <v>26.62008900065227</v>
+        <v>27.18950266911542</v>
       </c>
       <c r="D10" t="n">
-        <v>34.30717352490479</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.12136116689488</v>
+        <v>27.00984283923824</v>
       </c>
       <c r="D11" t="n">
-        <v>35.18387422479719</v>
+        <v>35.7169632282032</v>
       </c>
     </row>
     <row r="12">
@@ -6521,7 +6521,7 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.30021917551705</v>
+        <v>25.16808414607123</v>
       </c>
       <c r="D12" t="n">
         <v>34.06370009425158</v>
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>23.67484588791184</v>
       </c>
       <c r="D13" t="n">
-        <v>31.73990327829938</v>
+        <v>32.00006641992479</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>21.81737923147687</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -6566,7 +6566,7 @@
         <v>19.35024725070463</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -6577,10 +6577,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -6591,10 +6591,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -6605,10 +6605,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.457430421742454</v>
+        <v>7.504110844248433</v>
       </c>
       <c r="C21" t="n">
-        <v>83.89609224460261</v>
+        <v>86.29727470885697</v>
       </c>
       <c r="D21" t="n">
-        <v>6.525251619024647</v>
+        <v>7.504110844248433</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_6_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_6_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497626885457</v>
+        <v>10.84497627726797</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907172113131</v>
+        <v>37.78907175044762</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.984734005088556</v>
+        <v>0.9513135254151592</v>
       </c>
       <c r="C2" t="n">
-        <v>13.74250436404685</v>
+        <v>4.599487994396307</v>
       </c>
       <c r="D2" t="n">
-        <v>24.2550587811217</v>
+        <v>10.44775906859456</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.46314823669302</v>
+        <v>10.0187353218387</v>
       </c>
       <c r="C3" t="n">
-        <v>24.33752558827843</v>
+        <v>46.15195957664255</v>
       </c>
       <c r="D3" t="n">
-        <v>69.74335690969342</v>
+        <v>53.14691196940109</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.76412817573606</v>
+        <v>19.82050440103886</v>
       </c>
       <c r="C4" t="n">
-        <v>51.71454206890498</v>
+        <v>124.5130978342145</v>
       </c>
       <c r="D4" t="n">
-        <v>86.19941192827845</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>50.9281621578033</v>
+        <v>17.76963344686727</v>
       </c>
       <c r="C5" t="n">
-        <v>83.76762286485911</v>
+        <v>140.9544266372358</v>
       </c>
       <c r="D5" t="n">
-        <v>64.32901832077226</v>
+        <v>40.71798603363646</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>48.06047711369836</v>
+        <v>11.99499345048753</v>
       </c>
       <c r="C6" t="n">
-        <v>96.24170919501908</v>
+        <v>97.69076880648737</v>
       </c>
       <c r="D6" t="n">
-        <v>46.85292743747478</v>
+        <v>29.26295382048468</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>35.27321326588365</v>
+        <v>6.168320825782709</v>
       </c>
       <c r="C7" t="n">
-        <v>84.20057360243193</v>
+        <v>50.12509253572939</v>
       </c>
       <c r="D7" t="n">
-        <v>39.1059563032632</v>
+        <v>28.86534600026472</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19.02627050830318</v>
+        <v>6.091744504851458</v>
       </c>
       <c r="C8" t="n">
-        <v>56.57812019574367</v>
+        <v>29.79113408536946</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>31.04286240828414</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.764061755811273</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>35.38905949498476</v>
+        <v>31.17343485294896</v>
       </c>
       <c r="D9" t="n">
-        <v>34.27968458918587</v>
+        <v>35.16718451382499</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.694136684631501</v>
+        <v>3.4164820107789</v>
       </c>
       <c r="C10" t="n">
-        <v>30.17892442854695</v>
+        <v>30.03657101143117</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01894061048373</v>
+        <v>38.15071578703105</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>29.852984190737</v>
+        <v>30.91916219754903</v>
       </c>
       <c r="D11" t="n">
-        <v>36.42774856607789</v>
+        <v>37.6716229073586</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>27.98864530037232</v>
+        <v>23.86628669023996</v>
       </c>
       <c r="D12" t="n">
-        <v>34.49763257952867</v>
+        <v>37.75212621910684</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>26.27647730416588</v>
+        <v>20.03256190515617</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>35.90251354430586</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>27.3485457972034</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
+        <v>24.55547357862122</v>
+      </c>
+      <c r="D17" t="n">
         <v>17.9443845382232</v>
-      </c>
-      <c r="D17" t="n">
-        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>26.75262494072559</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>11.23610247510475</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>10.83260416865931</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>84.85539932116455</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.705614607394949</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>95.35698076651251</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.668816433319318</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.188176764045899</v>
+        <v>1.110356653503142</v>
       </c>
       <c r="C2" t="n">
-        <v>8.317366550378978</v>
+        <v>7.746971134211581</v>
       </c>
       <c r="D2" t="n">
-        <v>28.89872542220911</v>
+        <v>8.256498192715675</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.74294633240336</v>
+        <v>6.396086293167969</v>
       </c>
       <c r="C3" t="n">
-        <v>40.0307626406637</v>
+        <v>29.97766614917636</v>
       </c>
       <c r="D3" t="n">
-        <v>72.06028149171588</v>
+        <v>49.26409979910495</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.0283982346277</v>
+        <v>19.83326712119406</v>
       </c>
       <c r="C4" t="n">
-        <v>55.79861251857172</v>
+        <v>119.4845860930623</v>
       </c>
       <c r="D4" t="n">
-        <v>98.27294519510572</v>
+        <v>73.11762376918969</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>55.61600744558182</v>
+        <v>23.97918767622835</v>
       </c>
       <c r="C5" t="n">
-        <v>89.53539062730911</v>
+        <v>190.4345109312751</v>
       </c>
       <c r="D5" t="n">
-        <v>78.9079717288374</v>
+        <v>52.67076433284139</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>57.92213280285758</v>
+        <v>17.5899736169901</v>
       </c>
       <c r="C6" t="n">
-        <v>113.2681596297715</v>
+        <v>162.9387029784347</v>
       </c>
       <c r="D6" t="n">
-        <v>54.74225198880216</v>
+        <v>34.97868895460962</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>46.29234949834984</v>
+        <v>9.761517423326035</v>
       </c>
       <c r="C7" t="n">
-        <v>111.329207913884</v>
+        <v>95.33948305481626</v>
       </c>
       <c r="D7" t="n">
-        <v>43.47767883027424</v>
+        <v>31.14103717870882</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>28.03871443328891</v>
+        <v>6.592435834017332</v>
       </c>
       <c r="C8" t="n">
-        <v>82.78096642209104</v>
+        <v>47.73257338047992</v>
       </c>
       <c r="D8" t="n">
-        <v>38.63668090063322</v>
+        <v>31.96079651175491</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>13.64531134132641</v>
+        <v>6.212499472473814</v>
       </c>
       <c r="C9" t="n">
-        <v>52.47343304428775</v>
+        <v>35.16718451382499</v>
       </c>
       <c r="D9" t="n">
-        <v>36.0546844384641</v>
+        <v>35.49999698556465</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.117670855789377</v>
+        <v>4.128249096357838</v>
       </c>
       <c r="C10" t="n">
-        <v>36.01541453029424</v>
+        <v>34.30717352490479</v>
       </c>
       <c r="D10" t="n">
-        <v>35.44600086183109</v>
+        <v>38.86248287260999</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>32.87382187670443</v>
+        <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
-        <v>36.96083756948391</v>
+        <v>38.56010457970196</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>30.8092064546734</v>
+        <v>28.63954402828795</v>
       </c>
       <c r="D12" t="n">
-        <v>34.93156506480576</v>
+        <v>38.18605870438393</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>28.87810872041993</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>33.30088212805181</v>
+        <v>36.68300296918207</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>26.42668470291564</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>28.88498095434966</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.93362637120549</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>25.44199175555609</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.66578917439536</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>27.69215749368978</v>
+        <v>21.49242074137117</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>16.99994324673777</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>8.560839981032187</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>51.36503988619312</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>9.095892479846698</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>46.33947338815369</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.89268562860129</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>104.5780845789671</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9.865857035751612</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.629963230956964</v>
+        <v>0.600829594999048</v>
       </c>
       <c r="C2" t="n">
-        <v>7.127488332831843</v>
+        <v>3.326161221988194</v>
       </c>
       <c r="D2" t="n">
-        <v>30.19070540099791</v>
+        <v>5.640140560897926</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.5927799913826</v>
+        <v>5.929756133650734</v>
       </c>
       <c r="C3" t="n">
-        <v>36.00068831473054</v>
+        <v>32.1178761444344</v>
       </c>
       <c r="D3" t="n">
-        <v>76.60086462385738</v>
+        <v>47.04044124898592</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.66278717802039</v>
+        <v>21.28821721888784</v>
       </c>
       <c r="C4" t="n">
-        <v>75.87437132271475</v>
+        <v>112.9117852131299</v>
       </c>
       <c r="D4" t="n">
-        <v>108.023663393685</v>
+        <v>80.20093345533043</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>56.67138622764714</v>
+        <v>23.75829444277282</v>
       </c>
       <c r="C5" t="n">
-        <v>95.49950793060849</v>
+        <v>225.0656611985813</v>
       </c>
       <c r="D5" t="n">
-        <v>93.41329405908402</v>
+        <v>59.17484287347651</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>65.9322123218073</v>
+        <v>13.84656962069702</v>
       </c>
       <c r="C6" t="n">
-        <v>125.2631530802591</v>
+        <v>205.6457098608752</v>
       </c>
       <c r="D6" t="n">
-        <v>64.20139111922018</v>
+        <v>35.90447703971436</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>56.05386692167588</v>
+        <v>4.311835917051991</v>
       </c>
       <c r="C7" t="n">
-        <v>135.3437385074653</v>
+        <v>89.05138900911543</v>
       </c>
       <c r="D7" t="n">
-        <v>48.56804067679396</v>
+        <v>32.93763547748049</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>37.55184968744049</v>
+        <v>4.255876297909922</v>
       </c>
       <c r="C8" t="n">
-        <v>110.9865779651019</v>
+        <v>42.22496875965531</v>
       </c>
       <c r="D8" t="n">
-        <v>40.80634332701867</v>
+        <v>36.21667280966483</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19.85781081380023</v>
+        <v>2.884374755077128</v>
       </c>
       <c r="C9" t="n">
-        <v>74.43905617910588</v>
+        <v>26.18124777685393</v>
       </c>
       <c r="D9" t="n">
-        <v>37.71874679716245</v>
+        <v>40.38124657107979</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.680032363873552</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>47.83074815090461</v>
+        <v>26.33538216642069</v>
       </c>
       <c r="D10" t="n">
-        <v>36.01541453029424</v>
+        <v>30.17892442854695</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.686282702997524</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>36.78314123501524</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
-        <v>37.49392657288993</v>
+        <v>30.56376952861169</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>34.06370009425158</v>
+        <v>18.65909686691488</v>
       </c>
       <c r="D12" t="n">
-        <v>35.36549755008285</v>
+        <v>29.94134148411922</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>31.21957699504857</v>
+        <v>17.69109363052753</v>
       </c>
       <c r="D13" t="n">
-        <v>33.82120841130262</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>28.88498095434966</v>
+        <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>21.20280516861837</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>25.083653843506</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>30.10038461220721</v>
+        <v>17.91689560250429</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>21.90573652485908</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>27.69215749368978</v>
+        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>6.611089040398022</v>
       </c>
       <c r="C17" t="n">
-        <v>19.83326712119407</v>
+        <v>44.38874069981529</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>7.555530331883453</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>40.12893741108837</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>19.25796296650543</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.064112761277173</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>112.8975786578804</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11.08815504675611</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.720864856824416</v>
+        <v>0.3936808294029709</v>
       </c>
       <c r="C2" t="n">
-        <v>4.788965301315941</v>
+        <v>10.62741889847172</v>
       </c>
       <c r="D2" t="n">
-        <v>24.4985322117749</v>
+        <v>11.61702058435251</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>28.26451640526567</v>
+        <v>3.956443248114645</v>
       </c>
       <c r="C3" t="n">
-        <v>50.60418541540184</v>
+        <v>21.36773878293183</v>
       </c>
       <c r="D3" t="n">
-        <v>84.16523068507905</v>
+        <v>41.09105016125025</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.22288209105981</v>
+        <v>16.70640068316797</v>
       </c>
       <c r="C4" t="n">
-        <v>90.64083854229102</v>
+        <v>96.39682533229008</v>
       </c>
       <c r="D4" t="n">
-        <v>104.65430527271</v>
+        <v>85.03800439415447</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.13460691313561</v>
+        <v>27.85709110800325</v>
       </c>
       <c r="C5" t="n">
-        <v>74.83371875621313</v>
+        <v>218.6597574283709</v>
       </c>
       <c r="D5" t="n">
-        <v>64.35356201337844</v>
+        <v>73.43472827766143</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.77743067523902</v>
+        <v>21.53463589265379</v>
       </c>
       <c r="C6" t="n">
-        <v>89.11716610529999</v>
+        <v>282.9288891391841</v>
       </c>
       <c r="D6" t="n">
-        <v>31.95981476405067</v>
+        <v>44.19631814978292</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.852943133008</v>
+        <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>78.03225277664922</v>
+        <v>184.2710988440136</v>
       </c>
       <c r="D7" t="n">
-        <v>28.68568617038755</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.76901155206151</v>
+        <v>4.589670517353839</v>
       </c>
       <c r="C8" t="n">
-        <v>54.82570054366312</v>
+        <v>75.10369937488099</v>
       </c>
       <c r="D8" t="n">
-        <v>27.78836876870596</v>
+        <v>37.30150402285756</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.878124415953151</v>
+        <v>3.217187226816797</v>
       </c>
       <c r="C9" t="n">
-        <v>36.49843440078366</v>
+        <v>37.49687181600267</v>
       </c>
       <c r="D9" t="n">
-        <v>27.40156017323271</v>
+        <v>41.04687151455913</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.128249096357838</v>
+        <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>28.75539025738908</v>
+        <v>29.46715734296802</v>
       </c>
       <c r="D10" t="n">
-        <v>29.32480392585223</v>
+        <v>32.02951885105219</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>1.421570675749381</v>
       </c>
       <c r="C11" t="n">
-        <v>27.18753917370691</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>28.25371718051895</v>
+        <v>31.27455486648638</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>25.38505038870978</v>
+        <v>21.47965802121596</v>
       </c>
       <c r="D12" t="n">
-        <v>27.55471281509523</v>
+        <v>30.8092064546734</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
+        <v>21.07321447165778</v>
+      </c>
+      <c r="D13" t="n">
         <v>23.93500902953724</v>
-      </c>
-      <c r="D13" t="n">
-        <v>25.49598787928967</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
+        <v>21.20280516861837</v>
+      </c>
+      <c r="D14" t="n">
         <v>20.89551813718911</v>
-      </c>
-      <c r="D14" t="n">
-        <v>25.19753657719863</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.27523351455437</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>23.29196428325557</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>16.94594712300419</v>
+        <v>37.61173629739955</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>12.39947350463721</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>47.22206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>18.41660518396592</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.58662746324986</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>75.31968386981528</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.207189823325082</v>
+        <v>0.3259402378099411</v>
       </c>
       <c r="C2" t="n">
-        <v>2.589850443803086</v>
+        <v>5.42317431825938</v>
       </c>
       <c r="D2" t="n">
-        <v>17.32293824143497</v>
+        <v>8.926050127011999</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>29.95312245657018</v>
+        <v>2.837250865273282</v>
       </c>
       <c r="C3" t="n">
-        <v>34.43970946497811</v>
+        <v>31.9018916495001</v>
       </c>
       <c r="D3" t="n">
-        <v>84.52847733565038</v>
+        <v>40.96342295969816</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.06668639509333</v>
+        <v>13.50295792421063</v>
       </c>
       <c r="C4" t="n">
-        <v>111.878004880558</v>
+        <v>78.1971863909627</v>
       </c>
       <c r="D4" t="n">
-        <v>121.0161125116873</v>
+        <v>86.40361545076178</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.08614142272902</v>
+        <v>28.71612034921921</v>
       </c>
       <c r="C5" t="n">
-        <v>118.8651032916826</v>
+        <v>209.0877173119645</v>
       </c>
       <c r="D5" t="n">
-        <v>80.69966128908783</v>
+        <v>83.84125394267762</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.53970886209105</v>
+        <v>26.32458294167398</v>
       </c>
       <c r="C6" t="n">
-        <v>105.5800933578148</v>
+        <v>323.5428099161704</v>
       </c>
       <c r="D6" t="n">
-        <v>39.56737772425921</v>
+        <v>51.80388110999145</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>23.65521093382689</v>
+        <v>9.222537933694536</v>
       </c>
       <c r="C7" t="n">
-        <v>100.3699582913769</v>
+        <v>261.7643721310313</v>
       </c>
       <c r="D7" t="n">
-        <v>31.38058361854505</v>
+        <v>39.28561613314036</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.43245201595411</v>
+        <v>4.255876297909922</v>
       </c>
       <c r="C8" t="n">
-        <v>72.34989706446869</v>
+        <v>116.0769398116216</v>
       </c>
       <c r="D8" t="n">
-        <v>28.95664853675967</v>
+        <v>39.13737222979909</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.324999547834698</v>
+        <v>2.662499773917349</v>
       </c>
       <c r="C9" t="n">
-        <v>42.3781214015178</v>
+        <v>48.03593342109217</v>
       </c>
       <c r="D9" t="n">
-        <v>28.51093507903161</v>
+        <v>41.15780900513902</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.423534171157875</v>
       </c>
       <c r="C10" t="n">
         <v>32.02951885105219</v>
       </c>
       <c r="D10" t="n">
-        <v>30.32127784566274</v>
+        <v>32.88363935374691</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>30.38607319414302</v>
+        <v>27.18753917370691</v>
       </c>
       <c r="D11" t="n">
-        <v>29.49759152179966</v>
+        <v>32.87382187670443</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>22.1305567491316</v>
+        <v>22.99842171968578</v>
       </c>
       <c r="D12" t="n">
-        <v>28.63954402828795</v>
+        <v>29.29044275620359</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>17.17076734727672</v>
+        <v>17.43093048890212</v>
       </c>
       <c r="D13" t="n">
-        <v>26.27647730416588</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>16.59349969717959</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>14.33351648200343</v>
+        <v>31.89207417245764</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>40.5049467818149</v>
       </c>
       <c r="D16" t="n">
-        <v>15.70599977254047</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.16661937228147</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>65.59743635465912</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.631304831559704</v>
+        <v>1.012181883078461</v>
       </c>
       <c r="C2" t="n">
-        <v>4.070325981807276</v>
+        <v>9.369800089331559</v>
       </c>
       <c r="D2" t="n">
-        <v>15.63335044242621</v>
+        <v>11.59149514404209</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.70920705756047</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C3" t="n">
-        <v>21.35792130588936</v>
+        <v>26.33538216642069</v>
       </c>
       <c r="D3" t="n">
-        <v>79.0110552377833</v>
+        <v>38.74467314810038</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>48.49833658979244</v>
+        <v>9.686904597803279</v>
       </c>
       <c r="C4" t="n">
-        <v>98.40057239665781</v>
+        <v>78.74598335763666</v>
       </c>
       <c r="D4" t="n">
-        <v>134.3914432343459</v>
+        <v>86.86307337634929</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.50462798664542</v>
+        <v>25.69724615866027</v>
       </c>
       <c r="C5" t="n">
-        <v>162.601963515878</v>
+        <v>178.8008006359504</v>
       </c>
       <c r="D5" t="n">
-        <v>103.0344215607028</v>
+        <v>93.14331344041615</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>48.74475526355839</v>
+        <v>31.55729820530948</v>
       </c>
       <c r="C6" t="n">
-        <v>146.7172856611646</v>
+        <v>331.8749026821131</v>
       </c>
       <c r="D6" t="n">
-        <v>53.25294072145974</v>
+        <v>62.10830501376597</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>34.13536767666159</v>
+        <v>17.30723027816702</v>
       </c>
       <c r="C7" t="n">
-        <v>126.3008604036479</v>
+        <v>349.8575753808018</v>
       </c>
       <c r="D7" t="n">
-        <v>35.09355343600648</v>
+        <v>44.01665831990574</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>17.02350519163969</v>
+        <v>6.258641614573416</v>
       </c>
       <c r="C8" t="n">
-        <v>100.8058542720625</v>
+        <v>212.2096750114693</v>
       </c>
       <c r="D8" t="n">
-        <v>30.95941385342316</v>
+        <v>41.0566889916016</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.321874378272709</v>
+        <v>3.217187226816797</v>
       </c>
       <c r="C9" t="n">
-        <v>63.23436963053704</v>
+        <v>85.97655519941439</v>
       </c>
       <c r="D9" t="n">
-        <v>29.28749751309084</v>
+        <v>41.82343394861835</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.989421759431538</v>
+        <v>1.70824100538945</v>
       </c>
       <c r="C10" t="n">
-        <v>40.42837046088366</v>
+        <v>41.85190463204153</v>
       </c>
       <c r="D10" t="n">
-        <v>30.89069151412589</v>
+        <v>34.44952694202058</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>33.93999988351647</v>
+        <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
-        <v>30.20837685967435</v>
+        <v>33.40691088011046</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>26.68684784454105</v>
+        <v>26.03594911662541</v>
       </c>
       <c r="D12" t="n">
-        <v>29.07347651356504</v>
+        <v>29.94134148411922</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>19.77239876353076</v>
+        <v>20.03256190515617</v>
       </c>
       <c r="D13" t="n">
-        <v>26.53664044579129</v>
+        <v>24.45533531278805</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>16.59349969717959</v>
+        <v>20.58823110575986</v>
       </c>
       <c r="D14" t="n">
-        <v>20.28094407433061</v>
+        <v>17.20807376003809</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.5083653843506</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>32.96708790860789</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.0334615374024</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.87936820556466</v>
+        <v>40.09163099832699</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.11106066376691</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>11.33329549782518</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>35.50686921949439</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.322234231171206</v>
+        <v>0.6960591223109885</v>
       </c>
       <c r="C2" t="n">
-        <v>1.899681807717578</v>
+        <v>5.096252332745193</v>
       </c>
       <c r="D2" t="n">
-        <v>10.79038901737669</v>
+        <v>8.438121518001335</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.92519155249477</v>
+        <v>3.372303364087794</v>
       </c>
       <c r="C3" t="n">
-        <v>20.12091919853838</v>
+        <v>33.7328511179204</v>
       </c>
       <c r="D3" t="n">
-        <v>77.01810739816227</v>
+        <v>43.2901650187631</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>53.70552641311752</v>
+        <v>17.08928228782423</v>
       </c>
       <c r="C4" t="n">
-        <v>91.91711055781187</v>
+        <v>110.6783091859684</v>
       </c>
       <c r="D4" t="n">
-        <v>143.5678390259408</v>
+        <v>89.54324460894308</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52.15534678811181</v>
+        <v>18.94773069196344</v>
       </c>
       <c r="C5" t="n">
-        <v>190.4590546238812</v>
+        <v>274.5702891852267</v>
       </c>
       <c r="D5" t="n">
-        <v>112.0174130545611</v>
+        <v>86.12381735505146</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.45920555034281</v>
+        <v>10.74719211838983</v>
       </c>
       <c r="C6" t="n">
-        <v>181.7362262716483</v>
+        <v>305.2283064934462</v>
       </c>
       <c r="D6" t="n">
-        <v>52.48815925985148</v>
+        <v>55.94980166502573</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>11.25868267230242</v>
+        <v>4.132176087174825</v>
       </c>
       <c r="C7" t="n">
-        <v>133.6070268186527</v>
+        <v>149.2374320179661</v>
       </c>
       <c r="D7" t="n">
-        <v>35.45287309576081</v>
+        <v>34.91389360612931</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.006913291658733</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C8" t="n">
-        <v>78.1912959047372</v>
+        <v>63.33745313948297</v>
       </c>
       <c r="D8" t="n">
-        <v>32.12769362147687</v>
+        <v>30.79251674370121</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.107812321017901</v>
+        <v>1.220312396378785</v>
       </c>
       <c r="C9" t="n">
-        <v>30.84062238120929</v>
+        <v>31.94999728700819</v>
       </c>
       <c r="D9" t="n">
-        <v>32.39374724932775</v>
+        <v>26.29218526743382</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>26.62008900065227</v>
+        <v>24.62714116103124</v>
       </c>
       <c r="D10" t="n">
-        <v>23.63066724122073</v>
+        <v>26.1930287493049</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>21.32356013624072</v>
+        <v>20.7904711328347</v>
       </c>
       <c r="D11" t="n">
-        <v>23.27821981539612</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.05550195525234</v>
+        <v>16.27246819789088</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>19.96089432274615</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>16.91060420565131</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>14.04880964777186</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>27.65583282863265</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>8.296749848589794</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.541826921753</v>
+        <v>34.04210164475815</v>
       </c>
       <c r="D15" t="n">
-        <v>12.90016483380309</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.81278928812512</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9.506263020221864</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>30.22212132753381</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30.49799243242716</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.270602513473626</v>
+        <v>0.3809181092477624</v>
       </c>
       <c r="C2" t="n">
-        <v>2.710605411425443</v>
+        <v>3.008074965812227</v>
       </c>
       <c r="D2" t="n">
-        <v>10.90623524647782</v>
+        <v>6.12217868368311</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.80890335503714</v>
+        <v>2.891246989006857</v>
       </c>
       <c r="C3" t="n">
-        <v>13.33704256219292</v>
+        <v>26.3648345975481</v>
       </c>
       <c r="D3" t="n">
-        <v>68.70270434319178</v>
+        <v>40.09948497996098</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>50.01710028826225</v>
+        <v>11.24395645673872</v>
       </c>
       <c r="C4" t="n">
-        <v>71.49675830947821</v>
+        <v>94.16334930512858</v>
       </c>
       <c r="D4" t="n">
-        <v>148.4431981252305</v>
+        <v>86.78649705541802</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>64.84443586550184</v>
+        <v>17.52419652080557</v>
       </c>
       <c r="C5" t="n">
-        <v>181.9914806747525</v>
+        <v>216.3526503233909</v>
       </c>
       <c r="D5" t="n">
-        <v>133.8122120888403</v>
+        <v>87.10556505929826</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>53.65545728020094</v>
+        <v>10.54593383901924</v>
       </c>
       <c r="C6" t="n">
-        <v>238.2092994630376</v>
+        <v>302.1289289911389</v>
       </c>
       <c r="D6" t="n">
-        <v>71.20517924131691</v>
+        <v>57.39886127649402</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.01453059358123</v>
+        <v>3.413536767666159</v>
       </c>
       <c r="C7" t="n">
-        <v>192.4156777984451</v>
+        <v>195.8292145661113</v>
       </c>
       <c r="D7" t="n">
-        <v>40.48334833232147</v>
+        <v>33.0574086973986</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.009678608322226</v>
+        <v>1.084831213192726</v>
       </c>
       <c r="C8" t="n">
-        <v>119.8321247803657</v>
+        <v>74.35266238113219</v>
       </c>
       <c r="D8" t="n">
-        <v>34.13045893814036</v>
+        <v>26.70353755551324</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.773437264497239</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>56.02343274284421</v>
+        <v>30.17499743772996</v>
       </c>
       <c r="D9" t="n">
-        <v>33.28124717396686</v>
+        <v>20.63437324785945</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.423534171157875</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>31.31775176547326</v>
+        <v>17.50947030524187</v>
       </c>
       <c r="D10" t="n">
-        <v>25.19655482949439</v>
+        <v>19.92947839621025</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>24.87748682561417</v>
+        <v>13.32722508515045</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>17.41424077792992</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.44213062427633</v>
+        <v>11.71617710248143</v>
       </c>
       <c r="D12" t="n">
-        <v>21.91359050649305</v>
+        <v>13.4519070435898</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>15.86995163914969</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>8.065057390387548</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>14.13520344574558</v>
+        <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>2.765583282863265</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>24.38563122578652</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34.94432778496098</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.201479263548849</v>
+        <v>0.2748893571891069</v>
       </c>
       <c r="C2" t="n">
-        <v>2.171625921793944</v>
+        <v>11.24886519525995</v>
       </c>
       <c r="D2" t="n">
-        <v>8.249625958785947</v>
+        <v>6.752460709809561</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.61607989437726</v>
+        <v>2.042035224833366</v>
       </c>
       <c r="C3" t="n">
-        <v>12.15403657857551</v>
+        <v>17.9905266803228</v>
       </c>
       <c r="D3" t="n">
-        <v>63.26382206166446</v>
+        <v>35.83379120500858</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.60570694245383</v>
+        <v>8.308530821040756</v>
       </c>
       <c r="C4" t="n">
-        <v>56.5133248472634</v>
+        <v>78.42691535375644</v>
       </c>
       <c r="D4" t="n">
-        <v>149.4004021368711</v>
+        <v>87.32253130193681</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>71.17670855789376</v>
+        <v>17.64691498383642</v>
       </c>
       <c r="C5" t="n">
-        <v>168.516993433965</v>
+        <v>193.5515598922587</v>
       </c>
       <c r="D5" t="n">
-        <v>149.765612282851</v>
+        <v>98.2238578098934</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>63.87937787222722</v>
+        <v>16.90569546713008</v>
       </c>
       <c r="C6" t="n">
-        <v>267.2709950041517</v>
+        <v>328.0912470299459</v>
       </c>
       <c r="D6" t="n">
-        <v>84.52847733565039</v>
+        <v>70.56115274733101</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.57725195456389</v>
+        <v>7.545712854840985</v>
       </c>
       <c r="C7" t="n">
-        <v>246.7927196412674</v>
+        <v>319.4351775216017</v>
       </c>
       <c r="D7" t="n">
-        <v>45.57371017884118</v>
+        <v>40.90255460203486</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.674501730546564</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C8" t="n">
-        <v>156.6329374740573</v>
+        <v>163.8095131921015</v>
       </c>
       <c r="D8" t="n">
-        <v>36.04977569994287</v>
+        <v>29.2069942013426</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.107812321017901</v>
+        <v>0.6656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>67.00624431025328</v>
+        <v>60.01718240372024</v>
       </c>
       <c r="D9" t="n">
-        <v>33.05937219280708</v>
+        <v>22.40937309713768</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>32.59893251951534</v>
+        <v>26.33538216642069</v>
       </c>
       <c r="D10" t="n">
-        <v>25.62361508084176</v>
+        <v>20.64124548178919</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>24.6997904911455</v>
+        <v>16.52575910558656</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>17.94732978133594</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.7912318963607</v>
+        <v>13.23494080095125</v>
       </c>
       <c r="D12" t="n">
-        <v>20.61179305066178</v>
+        <v>14.10280577150543</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>11.70734137314322</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>8.585383673638358</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>11.67690719431156</v>
+        <v>3.072870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3481,10 +3481,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.901285450227578</v>
+        <v>0.2366011967234813</v>
       </c>
       <c r="C2" t="n">
-        <v>5.613633372883262</v>
+        <v>11.79078992800419</v>
       </c>
       <c r="D2" t="n">
-        <v>16.5748464907989</v>
+        <v>13.41558237853266</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.78373776762522</v>
+        <v>1.47753029489145</v>
       </c>
       <c r="C3" t="n">
-        <v>10.29362467902781</v>
+        <v>31.40610905885546</v>
       </c>
       <c r="D3" t="n">
-        <v>56.90209693814514</v>
+        <v>33.14380249537232</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.31368590593603</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C4" t="n">
-        <v>44.32492709903924</v>
+        <v>61.28658218531139</v>
       </c>
       <c r="D4" t="n">
-        <v>145.5843488104638</v>
+        <v>84.7827499910503</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>70.29313562407164</v>
+        <v>15.51161372709961</v>
       </c>
       <c r="C5" t="n">
-        <v>139.7272420069273</v>
+        <v>167.5597894223244</v>
       </c>
       <c r="D5" t="n">
-        <v>165.0072453912827</v>
+        <v>106.5932569885975</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>76.3976428490783</v>
+        <v>20.24658290468198</v>
       </c>
       <c r="C6" t="n">
-        <v>271.1754056239413</v>
+        <v>319.8799092316256</v>
       </c>
       <c r="D6" t="n">
-        <v>105.0568218314512</v>
+        <v>83.48193428292329</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>40.90255460203486</v>
+        <v>13.11516758103314</v>
       </c>
       <c r="C7" t="n">
-        <v>304.3437518119197</v>
+        <v>395.3115123397249</v>
       </c>
       <c r="D7" t="n">
-        <v>55.27534099220816</v>
+        <v>49.46633982617978</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.51590057081509</v>
+        <v>4.673119072214817</v>
       </c>
       <c r="C8" t="n">
-        <v>225.9786865635308</v>
+        <v>284.9768148502429</v>
       </c>
       <c r="D8" t="n">
-        <v>38.88702656521616</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3.106249736236907</v>
+        <v>1.220312396378785</v>
       </c>
       <c r="C9" t="n">
-        <v>113.9328028255466</v>
+        <v>124.9156143929556</v>
       </c>
       <c r="D9" t="n">
-        <v>34.27968458918587</v>
+        <v>24.4062479275757</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.8541205026947251</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>49.82369599052563</v>
+        <v>46.12250714551515</v>
       </c>
       <c r="D10" t="n">
-        <v>27.18950266911542</v>
+        <v>21.21065915025234</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>29.31989518733098</v>
+        <v>22.56743447752142</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>18.65811511921063</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>21.04572553593887</v>
+        <v>15.62156946997525</v>
       </c>
       <c r="D12" t="n">
-        <v>21.04572553593887</v>
+        <v>14.75370449942107</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.78864650614645</v>
+        <v>14.56913593102267</v>
       </c>
       <c r="D13" t="n">
-        <v>16.91060420565131</v>
+        <v>9.365873098514571</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.98419422574081</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>11.98419422574081</v>
+        <v>3.68744437715102</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>7.883434065101886</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.716536955379929</v>
+        <v>4.670173829102077</v>
       </c>
       <c r="C2" t="n">
-        <v>4.730060439061132</v>
+        <v>12.53102769700629</v>
       </c>
       <c r="D2" t="n">
-        <v>7.745989386507333</v>
+        <v>8.145560702135786</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.174391238457438</v>
+        <v>0.626355035309465</v>
       </c>
       <c r="C2" t="n">
-        <v>3.143556148998286</v>
+        <v>8.390997628197487</v>
       </c>
       <c r="D2" t="n">
-        <v>12.19821522526662</v>
+        <v>13.45681578211103</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.09499284760046</v>
+        <v>1.1388273369263</v>
       </c>
       <c r="C3" t="n">
-        <v>15.42816517223863</v>
+        <v>37.97400120026662</v>
       </c>
       <c r="D3" t="n">
-        <v>63.69088231301183</v>
+        <v>35.62762418711675</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>53.30988208830605</v>
+        <v>4.556291095409446</v>
       </c>
       <c r="C4" t="n">
-        <v>67.24677249779377</v>
+        <v>68.99526515905734</v>
       </c>
       <c r="D4" t="n">
-        <v>149.7449955810617</v>
+        <v>81.57930723209294</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.62672455487052</v>
+        <v>12.88543861823939</v>
       </c>
       <c r="C5" t="n">
-        <v>220.549621759046</v>
+        <v>141.4698441819654</v>
       </c>
       <c r="D5" t="n">
-        <v>151.7781950765569</v>
+        <v>111.4774518172253</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>25.39879485656924</v>
+        <v>20.56859615167493</v>
       </c>
       <c r="C6" t="n">
-        <v>256.2420412946431</v>
+        <v>298.3855249948459</v>
       </c>
       <c r="D6" t="n">
-        <v>82.75740447718914</v>
+        <v>93.82660984257193</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.60559946480004</v>
+        <v>17.66654993792135</v>
       </c>
       <c r="C7" t="n">
-        <v>158.8791762213741</v>
+        <v>427.5305084976967</v>
       </c>
       <c r="D7" t="n">
-        <v>34.91389360612931</v>
+        <v>59.16797063954677</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>2.086213871524472</v>
+        <v>8.344855486097888</v>
       </c>
       <c r="C8" t="n">
-        <v>83.94924619014475</v>
+        <v>383.6130066959199</v>
       </c>
       <c r="D8" t="n">
-        <v>25.20146356801562</v>
+        <v>36.88426124855267</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.5546874528994477</v>
+        <v>2.551562283337459</v>
       </c>
       <c r="C9" t="n">
-        <v>38.05155926890212</v>
+        <v>219.3234188764416</v>
       </c>
       <c r="D9" t="n">
-        <v>20.74531073843935</v>
+        <v>26.62499773917349</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>22.91890015564179</v>
+        <v>85.83911052081987</v>
       </c>
       <c r="D10" t="n">
-        <v>19.21771131063132</v>
+        <v>21.92242623583128</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>16.8811517745239</v>
+        <v>34.47308888692249</v>
       </c>
       <c r="D11" t="n">
-        <v>16.8811517745239</v>
+        <v>19.36890045708532</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>11.0652783745658</v>
+        <v>19.30999559483051</v>
       </c>
       <c r="D12" t="n">
-        <v>13.66887328622834</v>
+        <v>15.18763698469816</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.886199381765381</v>
+        <v>15.60978849752428</v>
       </c>
       <c r="D13" t="n">
-        <v>9.886199381765381</v>
+        <v>10.14636252339079</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>4.302018440009523</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>24.72531593145592</v>
+        <v>10.75013736150257</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>0.3583379120500857</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.214863878509809</v>
+        <v>4.852778902091983</v>
       </c>
       <c r="C2" t="n">
-        <v>4.288273972150068</v>
+        <v>11.84674954714626</v>
       </c>
       <c r="D2" t="n">
-        <v>20.83759502263855</v>
+        <v>12.43677991739859</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.38536918387927</v>
+        <v>7.716536955379929</v>
       </c>
       <c r="C3" t="n">
-        <v>11.91841712955628</v>
+        <v>24.74004214701962</v>
       </c>
       <c r="D3" t="n">
-        <v>9.64076245570368</v>
+        <v>8.605018627723293</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>3.632466505713199</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>8.197593330460869</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>5.75598678999905</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>14.49059611468292</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.78007281871549</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.7451308119901</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.3985356936788</v>
+        <v>11.67782862205892</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14527510220074</v>
+        <v>59.94618692656913</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576298316903388</v>
+        <v>0.7785219081372614</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.363287708300325</v>
+        <v>3.1857713002809</v>
       </c>
       <c r="C2" t="n">
-        <v>5.105088062083413</v>
+        <v>6.948810250658924</v>
       </c>
       <c r="D2" t="n">
-        <v>15.96910815727862</v>
+        <v>11.83693207010379</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.55427084673872</v>
+        <v>13.50393967191488</v>
       </c>
       <c r="C3" t="n">
-        <v>14.92256510455152</v>
+        <v>39.11282853719293</v>
       </c>
       <c r="D3" t="n">
-        <v>24.81367322483813</v>
+        <v>17.38675184221101</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>18.93987671032947</v>
+        <v>9.59756555671682</v>
       </c>
       <c r="C4" t="n">
+        <v>40.73860273542564</v>
+      </c>
+      <c r="D4" t="n">
         <v>18.71014774753571</v>
-      </c>
-      <c r="D4" t="n">
-        <v>20.12680968476386</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.043417883165113</v>
+        <v>2.454369260617026</v>
       </c>
       <c r="C5" t="n">
-        <v>5.375068680751288</v>
+        <v>5.056000676871074</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>25.72178985126644</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>5.514476854754335</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>13.8063179648229</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>30.06798693796707</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>6.767186925373263</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.40326162673396</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>6.926230053461247</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>20.36144738607885</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>20.85624822901923</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>22.91890015564179</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>24.87748682561417</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.57268737340794</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>40.32528695193774</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44144146787245</v>
+        <v>13.62803369114851</v>
       </c>
       <c r="C21" t="n">
-        <v>86.14698924181475</v>
+        <v>73.75171174033312</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250829782709991</v>
+        <v>1.60329808131159</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.048146695237099</v>
+        <v>3.326161221988194</v>
       </c>
       <c r="C2" t="n">
-        <v>5.499750639190632</v>
+        <v>5.786420968830701</v>
       </c>
       <c r="D2" t="n">
-        <v>18.66007861461912</v>
+        <v>18.23105486786327</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.87548227247668</v>
+        <v>12.14421910153304</v>
       </c>
       <c r="C3" t="n">
-        <v>17.91689560250429</v>
+        <v>31.49937509075891</v>
       </c>
       <c r="D3" t="n">
-        <v>31.82826057168159</v>
+        <v>23.12506717353362</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.77917318646925</v>
+        <v>19.64182631886593</v>
       </c>
       <c r="C4" t="n">
-        <v>29.69884980117026</v>
+        <v>76.16791388628454</v>
       </c>
       <c r="D4" t="n">
-        <v>28.02693346083794</v>
+        <v>23.4706423654285</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>16.39518666092174</v>
+        <v>9.032078879070657</v>
       </c>
       <c r="C5" t="n">
-        <v>21.94206118991621</v>
+        <v>47.14843349645307</v>
       </c>
       <c r="D5" t="n">
-        <v>29.67332436085985</v>
+        <v>26.65445017030091</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.876741757621407</v>
+        <v>4.467933802027235</v>
       </c>
       <c r="C6" t="n">
-        <v>12.19625172985813</v>
+        <v>10.54593383901924</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>31.95981476405067</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>6.94684675525043</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>20.00212772632452</v>
       </c>
       <c r="D7" t="n">
-        <v>37.42913122440964</v>
+        <v>32.81786225756237</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.34762080276138</v>
+        <v>7.510369937488099</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>23.86628669023996</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>33.96356182841841</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>29.50937249425062</v>
+        <v>23.96249796525614</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>36.49843440078366</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.537678946757763</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.69897297435728</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>6.397068040872215</v>
       </c>
       <c r="C11" t="n">
-        <v>31.27455486648638</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>44.42408361716816</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="D12" t="n">
-        <v>45.77987719673301</v>
+        <v>42.09145107187774</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>45.52854978444583</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73686262671233</v>
+        <v>14.83656359960278</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0948620229452</v>
+        <v>87.37087453099414</v>
       </c>
       <c r="D21" t="n">
-        <v>5.021058788013698</v>
+        <v>2.472760599933796</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.756968537703296</v>
+        <v>2.279618169261094</v>
       </c>
       <c r="C2" t="n">
-        <v>5.793293202760428</v>
+        <v>6.118251692866123</v>
       </c>
       <c r="D2" t="n">
-        <v>23.94384475887546</v>
+        <v>20.27898057892212</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.46176557836127</v>
+        <v>11.79569866652543</v>
       </c>
       <c r="C3" t="n">
-        <v>19.88529974951915</v>
+        <v>26.05067533218912</v>
       </c>
       <c r="D3" t="n">
-        <v>38.93120521190727</v>
+        <v>32.34367811641117</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.30168394930681</v>
+        <v>22.04121770804514</v>
       </c>
       <c r="C4" t="n">
-        <v>37.86699070050372</v>
+        <v>77.82706750646165</v>
       </c>
       <c r="D4" t="n">
-        <v>36.88426124855267</v>
+        <v>29.78818884225672</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.42221793275092</v>
+        <v>19.61041039233004</v>
       </c>
       <c r="C5" t="n">
-        <v>40.05530633326987</v>
+        <v>100.5064212222672</v>
       </c>
       <c r="D5" t="n">
-        <v>33.1830724035422</v>
+        <v>28.93701358267474</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>14.00757624419349</v>
+        <v>8.573602701187397</v>
       </c>
       <c r="C6" t="n">
-        <v>24.15099352447154</v>
+        <v>45.64537776125121</v>
       </c>
       <c r="D6" t="n">
-        <v>38.19882142453915</v>
+        <v>33.65038431076368</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.407867265618931</v>
       </c>
       <c r="C7" t="n">
-        <v>21.02020009562846</v>
+        <v>17.72643654788041</v>
       </c>
       <c r="D7" t="n">
-        <v>39.46527596301753</v>
+        <v>35.03366682604743</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>7.844164156932015</v>
       </c>
       <c r="C8" t="n">
-        <v>31.87734795689393</v>
+        <v>25.78560345204247</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>35.21529015133309</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>7.876561831172157</v>
       </c>
       <c r="C9" t="n">
-        <v>34.27968458918587</v>
+        <v>27.62343515439249</v>
       </c>
       <c r="D9" t="n">
-        <v>41.93437143919824</v>
+        <v>37.49687181600267</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>7.544731107136738</v>
       </c>
       <c r="C10" t="n">
-        <v>33.16834618797849</v>
+        <v>27.18950266911542</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.55661955724149</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9.062513057902304</v>
+        <v>6.75246070980956</v>
       </c>
       <c r="C11" t="n">
-        <v>33.7623035490478</v>
+        <v>28.43141351498762</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>45.13486895504285</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>34.49763257952867</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
-        <v>46.86470840992573</v>
+        <v>43.39324852770902</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>33.04071898642641</v>
+        <v>28.35778243716912</v>
       </c>
       <c r="D13" t="n">
-        <v>46.30903920932205</v>
+        <v>41.88626580169016</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>29.02537087605695</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>37.77765165941727</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.06672272143762</v>
+        <v>16.0744180384535</v>
       </c>
       <c r="C21" t="n">
-        <v>117.8638577541407</v>
+        <v>100.6766182408404</v>
       </c>
       <c r="D21" t="n">
-        <v>6.88256103673814</v>
+        <v>3.384088008095475</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.885397560510381</v>
+        <v>2.748893571891069</v>
       </c>
       <c r="C2" t="n">
-        <v>5.486006171331176</v>
+        <v>10.39081770174824</v>
       </c>
       <c r="D2" t="n">
-        <v>23.01412968295373</v>
+        <v>22.65677351860789</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.16094987023424</v>
+        <v>9.621127501618743</v>
       </c>
       <c r="C3" t="n">
-        <v>20.15037162966578</v>
+        <v>24.95602664195392</v>
       </c>
       <c r="D3" t="n">
-        <v>45.59727212374311</v>
+        <v>40.56090640095697</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.03594911662541</v>
+        <v>22.34752299177014</v>
       </c>
       <c r="C4" t="n">
-        <v>37.42029549507142</v>
+        <v>70.11838453271569</v>
       </c>
       <c r="D4" t="n">
-        <v>41.1214843400819</v>
+        <v>38.78590655167874</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26.23720739599601</v>
+        <v>26.55627539987623</v>
       </c>
       <c r="C5" t="n">
-        <v>41.94517066394498</v>
+        <v>123.8965602759475</v>
       </c>
       <c r="D5" t="n">
-        <v>31.66136346195964</v>
+        <v>32.66765485881262</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>16.02015903789946</v>
+        <v>17.34846368174539</v>
       </c>
       <c r="C6" t="n">
-        <v>30.18874190558942</v>
+        <v>104.6140536168359</v>
       </c>
       <c r="D6" t="n">
-        <v>30.87302005544945</v>
+        <v>35.54221213684728</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.347980655659875</v>
+        <v>8.444012004226815</v>
       </c>
       <c r="C7" t="n">
-        <v>18.20552942755285</v>
+        <v>42.27994663109313</v>
       </c>
       <c r="D7" t="n">
-        <v>31.14103717870882</v>
+        <v>37.12969817461437</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>7.760715602071035</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.20146356801562</v>
       </c>
       <c r="D8" t="n">
-        <v>30.37527396939631</v>
+        <v>36.63391558396972</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>8.209374302911826</v>
       </c>
       <c r="C9" t="n">
-        <v>22.2984356065578</v>
+        <v>30.28593492830985</v>
       </c>
       <c r="D9" t="n">
-        <v>29.95312245657017</v>
+        <v>38.49530923122167</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>7.971791358484101</v>
       </c>
       <c r="C10" t="n">
-        <v>21.49536598448391</v>
+        <v>30.7483380970101</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>44.55661955724149</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>7.107853378746905</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>30.56376952861169</v>
       </c>
       <c r="D11" t="n">
-        <v>34.47308888692249</v>
+        <v>45.66795795844887</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>31.24313893995049</v>
       </c>
       <c r="D12" t="n">
-        <v>32.11100391050467</v>
+        <v>44.47807974090174</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>30.43908757017236</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>42.14642894331557</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>28.88498095434966</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>27.69215749368978</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.605157496443535</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.063365983468009</v>
+        <v>17.33540104083403</v>
       </c>
       <c r="C21" t="n">
-        <v>66.21905609501259</v>
+        <v>114.4136468695046</v>
       </c>
       <c r="D21" t="n">
-        <v>5.297524487601007</v>
+        <v>4.333850260208506</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.722607368054658</v>
+        <v>1.832922963828795</v>
       </c>
       <c r="C2" t="n">
-        <v>5.486987919035423</v>
+        <v>15.51946770873358</v>
       </c>
       <c r="D2" t="n">
-        <v>29.0872209814245</v>
+        <v>19.19316761802514</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.75338570425158</v>
+        <v>9.400234268163208</v>
       </c>
       <c r="C3" t="n">
-        <v>21.00449213236051</v>
+        <v>33.10944132572368</v>
       </c>
       <c r="D3" t="n">
-        <v>54.39373155379454</v>
+        <v>48.23817344816703</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.16656261901924</v>
+        <v>20.20338600569511</v>
       </c>
       <c r="C4" t="n">
-        <v>45.83092807735385</v>
+        <v>66.04707680320416</v>
       </c>
       <c r="D4" t="n">
-        <v>56.2197822836936</v>
+        <v>49.12370987739765</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.28753857081986</v>
+        <v>30.09056713516474</v>
       </c>
       <c r="C5" t="n">
-        <v>58.51216317310991</v>
+        <v>126.57182277002</v>
       </c>
       <c r="D5" t="n">
-        <v>40.25165587411923</v>
+        <v>38.50905369908114</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>27.4113776502752</v>
+        <v>25.84156307118455</v>
       </c>
       <c r="C6" t="n">
-        <v>52.40765594810324</v>
+        <v>147.9650869932623</v>
       </c>
       <c r="D6" t="n">
-        <v>34.17365583712723</v>
+        <v>37.47429161880501</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>13.89369351050086</v>
+        <v>14.19312656029614</v>
       </c>
       <c r="C7" t="n">
-        <v>33.59638818703009</v>
+        <v>94.44118390543041</v>
       </c>
       <c r="D7" t="n">
-        <v>33.71616140694821</v>
+        <v>39.16584291322225</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.258641614573416</v>
+        <v>8.595201150680824</v>
       </c>
       <c r="C8" t="n">
-        <v>22.28076414788136</v>
+        <v>40.05530633326986</v>
       </c>
       <c r="D8" t="n">
-        <v>32.46148784092078</v>
+        <v>38.05254101660637</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>8.431249284071605</v>
       </c>
       <c r="C9" t="n">
-        <v>23.51874800293658</v>
+        <v>31.28437234352885</v>
       </c>
       <c r="D9" t="n">
-        <v>31.17343485294896</v>
+        <v>39.49374664644068</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>8.114144775599888</v>
       </c>
       <c r="C10" t="n">
-        <v>25.0542014123786</v>
+        <v>34.02246669067321</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>44.27191272300992</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
-        <v>35.00617789032851</v>
+        <v>46.55643963079223</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.292021036517808</v>
       </c>
       <c r="C12" t="n">
-        <v>22.34752299177014</v>
+        <v>32.97886888105885</v>
       </c>
       <c r="D12" t="n">
-        <v>33.41280136633594</v>
+        <v>45.34594471145593</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>21.33337761328319</v>
+        <v>32.780555844801</v>
       </c>
       <c r="D13" t="n">
-        <v>31.21957699504857</v>
+        <v>42.40659208494097</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>31.03599017435442</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>42.09832330580748</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.43836786437537</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>24.07245370813179</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.289726459358568</v>
+        <v>17.72607990046889</v>
       </c>
       <c r="C21" t="n">
-        <v>76.54212782326498</v>
+        <v>127.627775283376</v>
       </c>
       <c r="D21" t="n">
-        <v>6.378510651938748</v>
+        <v>5.317823970140668</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.075635630956009</v>
+        <v>1.785799074024948</v>
       </c>
       <c r="C2" t="n">
-        <v>6.862416452685205</v>
+        <v>9.683959354690538</v>
       </c>
       <c r="D2" t="n">
-        <v>25.22208026980481</v>
+        <v>15.23181563138926</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.56408832378119</v>
+        <v>13.02288329683394</v>
       </c>
       <c r="C3" t="n">
-        <v>21.23029410433728</v>
+        <v>54.2170169670301</v>
       </c>
       <c r="D3" t="n">
-        <v>65.04078540635119</v>
+        <v>52.17498174219674</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.11322944782042</v>
+        <v>14.44739921569606</v>
       </c>
       <c r="C4" t="n">
-        <v>49.92776124717579</v>
+        <v>103.7609148618454</v>
       </c>
       <c r="D4" t="n">
-        <v>70.32258805519903</v>
+        <v>46.92852201070178</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.28249096357838</v>
+        <v>14.55440971545897</v>
       </c>
       <c r="C5" t="n">
-        <v>73.77833997414781</v>
+        <v>88.40638076742529</v>
       </c>
       <c r="D5" t="n">
-        <v>52.05717201768713</v>
+        <v>33.47759671481624</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.31957639216151</v>
+        <v>8.774860980557992</v>
       </c>
       <c r="C6" t="n">
-        <v>74.66682164649117</v>
+        <v>62.18880832551422</v>
       </c>
       <c r="D6" t="n">
-        <v>39.48687441251096</v>
+        <v>25.76105975943631</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.13430381349934</v>
+        <v>5.689227946110266</v>
       </c>
       <c r="C7" t="n">
-        <v>57.49114556069321</v>
+        <v>28.14670668075605</v>
       </c>
       <c r="D7" t="n">
-        <v>36.05173919535137</v>
+        <v>26.70942804173872</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.18210635137117</v>
+        <v>5.841398840268521</v>
       </c>
       <c r="C8" t="n">
-        <v>34.96494448675015</v>
+        <v>23.03180114163017</v>
       </c>
       <c r="D8" t="n">
-        <v>34.63115026730623</v>
+        <v>29.04009709162065</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.990624491314035</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>26.5140602485936</v>
+        <v>25.95937279569415</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>33.72499713628642</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>27.18950266911542</v>
+        <v>26.33538216642069</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>36.44247478164161</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>27.00984283923824</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>35.7169632282032</v>
+        <v>36.25005223160922</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>25.16808414607123</v>
+        <v>26.68684784454105</v>
       </c>
       <c r="D12" t="n">
-        <v>34.06370009425158</v>
+        <v>34.49763257952867</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.67484588791184</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>34.86186097780424</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>21.81737923147687</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>34.10886048864694</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>32.6087499965578</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>30.58536797810513</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>25.97213551584937</v>
       </c>
     </row>
     <row r="18">
@@ -6602,10 +6602,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>31.29418982057133</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>13.23984953947248</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>13.4499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>96.83959354690535</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.504110844248433</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>86.29727470885697</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.504110844248433</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
